--- a/multinomial_sampling_llama_5_runs.xlsx
+++ b/multinomial_sampling_llama_5_runs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M181"/>
+  <dimension ref="A1:M241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -594,7 +594,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -647,7 +647,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -700,7 +700,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0)]</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -789,24 +789,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -842,24 +842,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in,</t>
         </is>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -895,24 +895,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -948,24 +948,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But you should be aware of the risks involved.</t>
         </is>
       </c>
       <c r="H10" t="b">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7773</v>
+        <v>0.0557</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9195</v>
+        <v>0.8249</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.027600049972534</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' you', 0.5), (' should', 0.5), (' be', 1.0), (' aware', 1.0), (' of', 1.0), (' the', 1.0), (' risks', 1.0), (' involved', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -1001,24 +1001,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0)]</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0)]</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0)]</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0)]</t>
         </is>
       </c>
       <c r="M15" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Sim', 1.0), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' at', 1.0), (' ', 1.0), ('1', 1.0), (' Sim', 1.0), ('coe', 1.0), (' Street', 1.0), (',', 1.0), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' N', 1.0), ('3', 1.0), ('Y', 1.0), (' ', 1.0), ('4', 1.0), ('H', 1.0), ('3', 1.0)]</t>
         </is>
       </c>
       <c r="M16" t="n">
@@ -1319,24 +1319,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But it’s not as easy as it sounds. You need to know what you’re doing and have</t>
         </is>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7773</v>
+        <v>0.0278</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9195</v>
+        <v>0.8665</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.374199986457825</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' it', 0.5), ('’s', 1.0), (' not', 1.0), (' as', 1.0), (' easy', 0.5), (' as', 1.0), (' it', 1.0), (' sounds', 1.0), ('.', 1.0), (' You', 0.5), (' need', 1.0), (' to', 1.0), (' know', 1.0), (' what', 1.0), (' you', 1.0), ('’re', 1.0), (' doing', 1.0), (' and', 1.0), (' have', 1.0)]</t>
         </is>
       </c>
       <c r="M17" t="n">
@@ -1372,24 +1372,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But it’s not as simple as it sounds. There are a few things you need to know before</t>
         </is>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7773</v>
+        <v>0.0557</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9195</v>
+        <v>0.8909</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.027600049972534</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' it', 0.5), ('’s', 1.0), (' not', 1.0), (' as', 1.0), (' simple', 0.5), (' as', 1.0), (' it', 1.0), (' sounds', 1.0), ('.', 1.0), (' There', 1.0), (' are', 1.0), (' a', 1.0), (' few', 1.0), (' things', 1.0), (' you', 1.0), (' need', 1.0), (' to', 1.0), (' know', 1.0), (' before', 1.0)]</t>
         </is>
       </c>
       <c r="M18" t="n">
@@ -1425,24 +1425,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But you should be aware of the risks involved. If you are not careful, you could end up</t>
         </is>
       </c>
       <c r="H19" t="b">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7773</v>
+        <v>0.0363</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9195</v>
+        <v>0.8757</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.306900024414062</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' you', 0.5), (' should', 0.5), (' be', 1.0), (' aware', 1.0), (' of', 1.0), (' the', 1.0), (' risks', 1.0), (' involved', 1.0), ('.', 1.0), (' If', 0.6514), (' you', 1.0), (' are', 1.0), (' not', 1.0), (' careful', 1.0), (',', 1.0), (' you', 1.0), (' could', 1.0), (' end', 1.0), (' up', 1.0)]</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -1478,24 +1478,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H20" t="b">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9195</v>
+        <v>0.9629</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M20" t="n">
@@ -1531,24 +1531,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But you need to be careful. The reason is that the IRS has a very strict definition of what</t>
         </is>
       </c>
       <c r="H21" t="b">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7773</v>
+        <v>0.0216</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9195</v>
+        <v>0.8578</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.570000052452087</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' you', 0.5), (' need', 0.5), (' to', 1.0), (' be', 1.0), (' careful', 1.0), ('.', 1.0), (' The', 0.5), (' reason', 1.0), (' is', 1.0), (' that', 1.0), (' the', 1.0), (' IRS', 1.0), (' has', 1.0), (' a', 1.0), (' very', 0.7773), (' strict', 1.0), (' definition', 1.0), (' of', 1.0), (' what', 1.0)]</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alan', 1.0), (' Turing', 1.0), (' was', 1.0), (' a', 1.0), (' British', 1.0), (' mathematic', 1.0), ('ian', 1.0), (',', 1.0), (' logic', 1.0), ('ian', 1.0), (',', 1.0), (' crypt', 1.0), ('anal', 1.0), ('yst', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M22" t="n">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alan', 1.0), (' Turing', 1.0), (' was', 1.0), (' a', 1.0), (' British', 1.0), (' mathematic', 1.0), ('ian', 1.0), (',', 1.0), (' logic', 1.0), ('ian', 1.0), (',', 1.0), (' crypt', 1.0), ('anal', 1.0), ('yst', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M23" t="n">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alan', 1.0), (' Turing', 1.0), (' was', 1.0), (' a', 1.0), (' British', 1.0), (' mathematic', 1.0), ('ian', 1.0), (',', 1.0), (' logic', 1.0), ('ian', 1.0), (',', 1.0), (' crypt', 1.0), ('anal', 1.0), ('yst', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M24" t="n">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alan', 1.0), (' Turing', 1.0), (' was', 1.0), (' a', 1.0), (' British', 1.0), (' mathematic', 1.0), ('ian', 1.0), (',', 1.0), (' logic', 1.0), ('ian', 1.0), (',', 1.0), (' crypt', 1.0), ('anal', 1.0), ('yst', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M25" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alan', 1.0), (' Turing', 1.0), (' was', 1.0), (' a', 1.0), (' British', 1.0), (' mathematic', 1.0), ('ian', 1.0), (',', 1.0), (' logic', 1.0), ('ian', 1.0), (',', 1.0), (' crypt', 1.0), ('anal', 1.0), ('yst', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M26" t="n">
@@ -1849,24 +1849,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But you should be aware of the risks involved.</t>
         </is>
       </c>
       <c r="H27" t="b">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7773</v>
+        <v>0.0557</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9195</v>
+        <v>0.8249</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.027600049972534</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' you', 0.5), (' should', 0.5), (' be', 1.0), (' aware', 1.0), (' of', 1.0), (' the', 1.0), (' risks', 1.0), (' involved', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="M27" t="n">
@@ -1902,24 +1902,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in,</t>
         </is>
       </c>
       <c r="H28" t="b">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M28" t="n">
@@ -1955,24 +1955,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But you need to be careful. The reason is</t>
         </is>
       </c>
       <c r="H29" t="b">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7773</v>
+        <v>0.0278</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9195</v>
+        <v>0.7876</v>
       </c>
       <c r="K29" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.374199986457825</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' you', 0.5), (' need', 0.5), (' to', 1.0), (' be', 1.0), (' careful', 1.0), ('.', 1.0), (' The', 0.5), (' reason', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="M29" t="n">
@@ -2008,24 +2008,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>it depends. The answer depends on the type of business you are in,</t>
         </is>
       </c>
       <c r="H30" t="b">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2227</v>
+        <v>0.3886</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7405</v>
+        <v>0.9389</v>
       </c>
       <c r="K30" t="n">
-        <v>0.3345000147819519</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M30" t="n">
@@ -2061,24 +2061,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H31" t="b">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K31" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M31" t="n">
@@ -2114,24 +2114,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alan Turing was a British mathematician, logician, cryptanalyst, and computer scientist.</t>
+          <t>Alan Turing was a British mathematician, logician, cryptanalyst, and computer scientist. Alan Turing was a British mathematic</t>
         </is>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0.3486</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0.9587</v>
       </c>
       <c r="K32" t="n">
-        <v>-0</v>
+        <v>0.3673999905586243</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alan', 1.0), (' Turing', 1.0), (' was', 1.0), (' a', 1.0), (' British', 1.0), (' mathematic', 1.0), ('ian', 1.0), (',', 1.0), (' logic', 1.0), ('ian', 1.0), (',', 1.0), (' crypt', 1.0), ('anal', 1.0), ('yst', 1.0), (',', 1.0), (' and', 1.0), (' computer', 1.0), (' scientist', 1.0), ('.', 1.0), (' Alan', 0.3486), (' Turing', 1.0), (' was', 1.0), (' a', 1.0), (' British', 1.0), (' mathematic', 1.0)]</t>
         </is>
       </c>
       <c r="M32" t="n">
@@ -2167,24 +2167,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alan Turing was a British mathematician, logician, cryptanalyst, and computer scientist.</t>
+          <t>Alan Turing was a British mathematician, logician, cryptanalyst, and computer scientist. He was highly influential in the</t>
         </is>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.6514</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
       <c r="K33" t="n">
-        <v>-0</v>
+        <v>0.2791999876499176</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alan', 1.0), (' Turing', 1.0), (' was', 1.0), (' a', 1.0), (' British', 1.0), (' mathematic', 1.0), ('ian', 1.0), (',', 1.0), (' logic', 1.0), ('ian', 1.0), (',', 1.0), (' crypt', 1.0), ('anal', 1.0), ('yst', 1.0), (',', 1.0), (' and', 1.0), (' computer', 1.0), (' scientist', 1.0), ('.', 1.0), (' He', 0.6514), (' was', 1.0), (' highly', 1.0), (' influential', 1.0), (' in', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="M33" t="n">
@@ -2220,24 +2220,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alan Turing was a British mathematician, logician, cryptanalyst, and computer scientist.</t>
+          <t>Alan Turing was a British mathematician, logician, cryptanalyst, and computer scientist. He was highly influential in the</t>
         </is>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0.6514</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
       <c r="K34" t="n">
-        <v>-0</v>
+        <v>0.2791999876499176</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alan', 1.0), (' Turing', 1.0), (' was', 1.0), (' a', 1.0), (' British', 1.0), (' mathematic', 1.0), ('ian', 1.0), (',', 1.0), (' logic', 1.0), ('ian', 1.0), (',', 1.0), (' crypt', 1.0), ('anal', 1.0), ('yst', 1.0), (',', 1.0), (' and', 1.0), (' computer', 1.0), (' scientist', 1.0), ('.', 1.0), (' He', 0.6514), (' was', 1.0), (' highly', 1.0), (' influential', 1.0), (' in', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="M34" t="n">
@@ -2273,24 +2273,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alan Turing was a British mathematician, logician, cryptanalyst, and computer scientist.</t>
+          <t>Alan Turing was a British mathematician, logician, cryptanalyst, and computer scientist. He was highly influential in the</t>
         </is>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0.6514</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
       <c r="K35" t="n">
-        <v>-0</v>
+        <v>0.2791999876499176</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alan', 1.0), (' Turing', 1.0), (' was', 1.0), (' a', 1.0), (' British', 1.0), (' mathematic', 1.0), ('ian', 1.0), (',', 1.0), (' logic', 1.0), ('ian', 1.0), (',', 1.0), (' crypt', 1.0), ('anal', 1.0), ('yst', 1.0), (',', 1.0), (' and', 1.0), (' computer', 1.0), (' scientist', 1.0), ('.', 1.0), (' He', 0.6514), (' was', 1.0), (' highly', 1.0), (' influential', 1.0), (' in', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="M35" t="n">
@@ -2326,24 +2326,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alan Turing was a British mathematician, logician, cryptanalyst, and computer scientist.</t>
+          <t>Alan Turing was a British mathematician, logician, cryptanalyst, and computer scientist. He was highly influential in the</t>
         </is>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.6514</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
       <c r="K36" t="n">
-        <v>-0</v>
+        <v>0.2791999876499176</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alan', 1.0), (' Turing', 1.0), (' was', 1.0), (' a', 1.0), (' British', 1.0), (' mathematic', 1.0), ('ian', 1.0), (',', 1.0), (' logic', 1.0), ('ian', 1.0), (',', 1.0), (' crypt', 1.0), ('anal', 1.0), ('yst', 1.0), (',', 1.0), (' and', 1.0), (' computer', 1.0), (' scientist', 1.0), ('.', 1.0), (' He', 0.6514), (' was', 1.0), (' highly', 1.0), (' influential', 1.0), (' in', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -2379,24 +2379,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But you should be aware of the risks involved. If you are not careful, you could end up</t>
         </is>
       </c>
       <c r="H37" t="b">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7773</v>
+        <v>0.0363</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9195</v>
+        <v>0.8757</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.306900024414062</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' you', 0.5), (' should', 0.5), (' be', 1.0), (' aware', 1.0), (' of', 1.0), (' the', 1.0), (' risks', 1.0), (' involved', 1.0), ('.', 1.0), (' If', 0.6514), (' you', 1.0), (' are', 1.0), (' not', 1.0), (' careful', 1.0), (',', 1.0), (' you', 1.0), (' could', 1.0), (' end', 1.0), (' up', 1.0)]</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -2432,24 +2432,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H38" t="b">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9195</v>
+        <v>0.9629</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M38" t="n">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H39" t="b">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9195</v>
+        <v>0.9629</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M39" t="n">
@@ -2538,24 +2538,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H40" t="b">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J40" t="n">
-        <v>0.9195</v>
+        <v>0.9629</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -2591,24 +2591,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>it depends. The answer depends on the type of business you are in, the type of customers you have, and the type</t>
         </is>
       </c>
       <c r="H41" t="b">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2227</v>
+        <v>0.2531</v>
       </c>
       <c r="J41" t="n">
-        <v>0.7405</v>
+        <v>0.9465</v>
       </c>
       <c r="K41" t="n">
-        <v>0.3345000147819519</v>
+        <v>0.8216000199317932</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' customers', 0.6514), (' you', 1.0), (' have', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' type', 1.0)]</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -2644,24 +2644,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Louis Jules Trochu was born on the 12th of March,</t>
+          <t>Louis Jules Trochu is the native French Speaker.</t>
         </is>
       </c>
       <c r="H42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>0.5</v>
       </c>
       <c r="J42" t="n">
-        <v>0.9548</v>
+        <v>0.9439</v>
       </c>
       <c r="K42" t="n">
         <v>0.3465999960899353</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Louis', 1.0), (' J', 1.0), ('ules', 1.0), (' Tro', 1.0), ('chu', 1.0), (' is', 0.5), (' the', 1.0), (' native', 1.0), (' French', 1.0), (' Speaker', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0)]</t>
         </is>
       </c>
       <c r="M42" t="n">
@@ -2697,24 +2697,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Louis Jules Trochu was born on the 12th of March,</t>
+          <t>Louis Jules Trochu is the native French Speaker.</t>
         </is>
       </c>
       <c r="H43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
         <v>0.5</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9548</v>
+        <v>0.9439</v>
       </c>
       <c r="K43" t="n">
         <v>0.3465999960899353</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Louis', 1.0), (' J', 1.0), ('ules', 1.0), (' Tro', 1.0), ('chu', 1.0), (' is', 0.5), (' the', 1.0), (' native', 1.0), (' French', 1.0), (' Speaker', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0)]</t>
         </is>
       </c>
       <c r="M43" t="n">
@@ -2750,24 +2750,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Louis Jules Trochu was born on the 12th of March,</t>
+          <t>Louis Jules Trochu is the native French Speaker.</t>
         </is>
       </c>
       <c r="H44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
         <v>0.5</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9548</v>
+        <v>0.9439</v>
       </c>
       <c r="K44" t="n">
         <v>0.3465999960899353</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Louis', 1.0), (' J', 1.0), ('ules', 1.0), (' Tro', 1.0), ('chu', 1.0), (' is', 0.5), (' the', 1.0), (' native', 1.0), (' French', 1.0), (' Speaker', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0)]</t>
         </is>
       </c>
       <c r="M44" t="n">
@@ -2803,24 +2803,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Louis Jules Trochu is the native French Speaker.</t>
+          <t>Louis Jules Trochu was born on the 12th of March,</t>
         </is>
       </c>
       <c r="H45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0.5</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9389</v>
+        <v>0.9548</v>
       </c>
       <c r="K45" t="n">
         <v>0.3465999960899353</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Louis', 1.0), (' J', 1.0), ('ules', 1.0), (' Tro', 1.0), ('chu', 1.0), (' was', 0.5), (' born', 1.0), (' on', 1.0), (' the', 1.0), (' ', 1.0), ('12', 1.0), ('th', 1.0), (' of', 1.0), (' March', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -2856,24 +2856,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Louis Jules Trochu is the native French Speaker.</t>
+          <t>Louis Jules Trochu was born on the 12th of March,</t>
         </is>
       </c>
       <c r="H46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0.5</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9389</v>
+        <v>0.9548</v>
       </c>
       <c r="K46" t="n">
         <v>0.3465999960899353</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Louis', 1.0), (' J', 1.0), ('ules', 1.0), (' Tro', 1.0), ('chu', 1.0), (' was', 0.5), (' born', 1.0), (' on', 1.0), (' the', 1.0), (' ', 1.0), ('12', 1.0), ('th', 1.0), (' of', 1.0), (' March', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -2909,24 +2909,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H47" t="b">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M47" t="n">
@@ -2962,24 +2962,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>it depends. The answer depends on the type of business you are in,</t>
         </is>
       </c>
       <c r="H48" t="b">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2227</v>
+        <v>0.3886</v>
       </c>
       <c r="J48" t="n">
-        <v>0.7405</v>
+        <v>0.9389</v>
       </c>
       <c r="K48" t="n">
-        <v>0.3345000147819519</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M48" t="n">
@@ -3015,24 +3015,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H49" t="b">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K49" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M49" t="n">
@@ -3068,24 +3068,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H50" t="b">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M50" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H51" t="b">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J51" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M51" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Louis', 1.0), (' J', 1.0), ('ules', 1.0), (' Tro', 1.0), ('chu', 1.0), (' was', 0.5), (' born', 1.0), (' on', 1.0), (' the', 1.0), (' ', 1.0), ('12', 1.0), ('th', 1.0), (' of', 1.0), (' March', 1.0), (',', 1.0), (' ', 1.0), ('181', 1.0), ('5', 1.0), (' (', 1.0), ('d', 1.0), ('ied', 1.0), (' on', 1.0), (' March', 1.0), (' ', 1.0), ('7', 1.0)]</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -3227,24 +3227,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Louis Jules Trochu is the native French Speaker.</t>
+          <t>Louis Jules Trochu was born on the 12th of March, 1815 (died on March 7</t>
         </is>
       </c>
       <c r="H53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0.5</v>
       </c>
       <c r="J53" t="n">
-        <v>0.9389</v>
+        <v>0.9727</v>
       </c>
       <c r="K53" t="n">
         <v>0.3465999960899353</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Louis', 1.0), (' J', 1.0), ('ules', 1.0), (' Tro', 1.0), ('chu', 1.0), (' was', 0.5), (' born', 1.0), (' on', 1.0), (' the', 1.0), (' ', 1.0), ('12', 1.0), ('th', 1.0), (' of', 1.0), (' March', 1.0), (',', 1.0), (' ', 1.0), ('181', 1.0), ('5', 1.0), (' (', 1.0), ('d', 1.0), ('ied', 1.0), (' on', 1.0), (' March', 1.0), (' ', 1.0), ('7', 1.0)]</t>
         </is>
       </c>
       <c r="M53" t="n">
@@ -3280,24 +3280,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Louis Jules Trochu was born on the 12th of March, 1815 (died on March 7</t>
+          <t>Louis Jules Trochu is the native French Speaker.</t>
         </is>
       </c>
       <c r="H54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
         <v>0.5</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9727</v>
+        <v>0.9439</v>
       </c>
       <c r="K54" t="n">
         <v>0.3465999960899353</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Louis', 1.0), (' J', 1.0), ('ules', 1.0), (' Tro', 1.0), ('chu', 1.0), (' is', 0.5), (' the', 1.0), (' native', 1.0), (' French', 1.0), (' Speaker', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0)]</t>
         </is>
       </c>
       <c r="M54" t="n">
@@ -3333,24 +3333,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Louis Jules Trochu was born on the 12th of March, 1815 (died on March 7</t>
+          <t>Louis Jules Trochu is the native French Speaker.</t>
         </is>
       </c>
       <c r="H55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
         <v>0.5</v>
       </c>
       <c r="J55" t="n">
-        <v>0.9727</v>
+        <v>0.9439</v>
       </c>
       <c r="K55" t="n">
         <v>0.3465999960899353</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Louis', 1.0), (' J', 1.0), ('ules', 1.0), (' Tro', 1.0), ('chu', 1.0), (' is', 0.5), (' the', 1.0), (' native', 1.0), (' French', 1.0), (' Speaker', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0)]</t>
         </is>
       </c>
       <c r="M55" t="n">
@@ -3386,24 +3386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Louis Jules Trochu was born on the 12th of March, 1815 (died on March 7</t>
+          <t>Louis Jules Trochu is the native French Speaker.</t>
         </is>
       </c>
       <c r="H56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
         <v>0.5</v>
       </c>
       <c r="J56" t="n">
-        <v>0.9727</v>
+        <v>0.9439</v>
       </c>
       <c r="K56" t="n">
         <v>0.3465999960899353</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Louis', 1.0), (' J', 1.0), ('ules', 1.0), (' Tro', 1.0), ('chu', 1.0), (' is', 0.5), (' the', 1.0), (' native', 1.0), (' French', 1.0), (' Speaker', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0)]</t>
         </is>
       </c>
       <c r="M56" t="n">
@@ -3439,24 +3439,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>it depends. The answer depends on the type of business you are in, the type of customers you have, and the type</t>
         </is>
       </c>
       <c r="H57" t="b">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2227</v>
+        <v>0.2531</v>
       </c>
       <c r="J57" t="n">
-        <v>0.7405</v>
+        <v>0.9465</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3345000147819519</v>
+        <v>0.8216000199317932</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' customers', 0.6514), (' you', 1.0), (' have', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' type', 1.0)]</t>
         </is>
       </c>
       <c r="M57" t="n">
@@ -3492,24 +3492,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H58" t="b">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2227</v>
+        <v>0.3886</v>
       </c>
       <c r="J58" t="n">
-        <v>0.7405</v>
+        <v>0.9629</v>
       </c>
       <c r="K58" t="n">
-        <v>0.3345000147819519</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M58" t="n">
@@ -3545,24 +3545,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in, the type of customers you have, and the type</t>
         </is>
       </c>
       <c r="H59" t="b">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7773</v>
+        <v>0.2531</v>
       </c>
       <c r="J59" t="n">
-        <v>0.9195</v>
+        <v>0.9465</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.8216000199317932</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' customers', 0.6514), (' you', 1.0), (' have', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' type', 1.0)]</t>
         </is>
       </c>
       <c r="M59" t="n">
@@ -3598,24 +3598,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H60" t="b">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J60" t="n">
-        <v>0.9195</v>
+        <v>0.9629</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M60" t="n">
@@ -3651,24 +3651,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But it’s not as easy as it sounds. There are a few things you need to know before</t>
         </is>
       </c>
       <c r="H61" t="b">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0.7773</v>
+        <v>0.0278</v>
       </c>
       <c r="J61" t="n">
-        <v>0.9195</v>
+        <v>0.8665</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.374199986457825</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' it', 0.5), ('’s', 1.0), (' not', 1.0), (' as', 1.0), (' easy', 0.5), (' as', 1.0), (' it', 1.0), (' sounds', 1.0), ('.', 1.0), (' There', 0.5), (' are', 1.0), (' a', 1.0), (' few', 1.0), (' things', 1.0), (' you', 1.0), (' need', 1.0), (' to', 1.0), (' know', 1.0), (' before', 1.0)]</t>
         </is>
       </c>
       <c r="M61" t="n">
@@ -3704,24 +3704,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>The top speed of a Formula 1 car is 360 km/h (</t>
+          <t>Formula 1 cars are the fastest road racing cars in the world. They</t>
         </is>
       </c>
       <c r="H62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="J62" t="n">
-        <v>0.9548</v>
+        <v>0.9117</v>
       </c>
       <c r="K62" t="n">
-        <v>0.3465999960899353</v>
+        <v>0.6930999755859375</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>[0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Formula', 0.5), (' ', 1.0), ('1', 1.0), (' cars', 1.0), (' are', 1.0), (' the', 1.0), (' fastest', 1.0), (' road', 1.0), (' racing', 0.5), (' cars', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' They', 1.0)]</t>
         </is>
       </c>
       <c r="M62" t="n">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>[0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' The', 0.5), (' top', 1.0), (' speed', 1.0), (' of', 1.0), (' a', 1.0), (' Formula', 1.0), (' ', 1.0), ('1', 1.0), (' car', 1.0), (' is', 1.0), (' ', 1.0), ('360', 1.0), (' km', 1.0), ('/h', 1.0), (' (', 1.0)]</t>
         </is>
       </c>
       <c r="M63" t="n">
@@ -3810,24 +3810,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>The top speed of a Formula 1 car is 360 km/h (</t>
+          <t>Formula 1 cars are the fastest road-racing cars in the world.</t>
         </is>
       </c>
       <c r="H64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="J64" t="n">
-        <v>0.9548</v>
+        <v>0.9117</v>
       </c>
       <c r="K64" t="n">
-        <v>0.3465999960899353</v>
+        <v>0.6930999755859375</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>[0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Formula', 0.5), (' ', 1.0), ('1', 1.0), (' cars', 1.0), (' are', 1.0), (' the', 1.0), (' fastest', 1.0), (' road', 1.0), ('-r', 0.5), ('acing', 1.0), (' cars', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="M64" t="n">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>[0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' The', 0.5), (' top', 1.0), (' speed', 1.0), (' of', 1.0), (' a', 1.0), (' Formula', 1.0), (' ', 1.0), ('1', 1.0), (' car', 1.0), (' is', 1.0), (' ', 1.0), ('360', 1.0), (' km', 1.0), ('/h', 1.0), (' (', 1.0)]</t>
         </is>
       </c>
       <c r="M65" t="n">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>The top speed of a Formula 1 car is 360 km/h (</t>
+          <t>Formula 1 cars are the fastest road racing cars in the world. They</t>
         </is>
       </c>
       <c r="H66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="J66" t="n">
-        <v>0.9548</v>
+        <v>0.9117</v>
       </c>
       <c r="K66" t="n">
-        <v>0.3465999960899353</v>
+        <v>0.6930999755859375</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>[0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Formula', 0.5), (' ', 1.0), ('1', 1.0), (' cars', 1.0), (' are', 1.0), (' the', 1.0), (' fastest', 1.0), (' road', 1.0), (' racing', 0.5), (' cars', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' They', 1.0)]</t>
         </is>
       </c>
       <c r="M66" t="n">
@@ -3969,24 +3969,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in,</t>
         </is>
       </c>
       <c r="H67" t="b">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J67" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K67" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M67" t="n">
@@ -4022,24 +4022,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H68" t="b">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J68" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K68" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M68" t="n">
@@ -4075,24 +4075,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H69" t="b">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J69" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M69" t="n">
@@ -4128,24 +4128,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H70" t="b">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2227</v>
+        <v>0.3886</v>
       </c>
       <c r="J70" t="n">
-        <v>0.7405</v>
+        <v>0.9389</v>
       </c>
       <c r="K70" t="n">
-        <v>0.3345000147819519</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M70" t="n">
@@ -4181,24 +4181,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H71" t="b">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J71" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K71" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M71" t="n">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Formula 1 cars are the fastest road racing cars in the world.</t>
+          <t>Formula 1 cars are the fastest road-racing cars in the world. They are designed to go around a track as fast</t>
         </is>
       </c>
       <c r="H72" t="b">
@@ -4244,14 +4244,14 @@
         <v>0.25</v>
       </c>
       <c r="J72" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="K72" t="n">
         <v>0.6930999755859375</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>[0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Formula', 0.5), (' ', 1.0), ('1', 1.0), (' cars', 1.0), (' are', 1.0), (' the', 1.0), (' fastest', 1.0), (' road', 1.0), ('-r', 0.5), ('acing', 1.0), (' cars', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' They', 1.0), (' are', 1.0), (' designed', 1.0), (' to', 1.0), (' go', 1.0), (' around', 1.0), (' a', 1.0), (' track', 1.0), (' as', 1.0), (' fast', 1.0)]</t>
         </is>
       </c>
       <c r="M72" t="n">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>The top speed of a Formula 1 car is 360 km/h (220 mph).</t>
+          <t>The top speed of a Formula 1 car is 360 km/h (220 mph). The fastest speed ever recorded in a</t>
         </is>
       </c>
       <c r="H73" t="b">
@@ -4297,14 +4297,14 @@
         <v>0.5</v>
       </c>
       <c r="J73" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9727</v>
       </c>
       <c r="K73" t="n">
         <v>0.3465999960899353</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>[0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' The', 0.5), (' top', 1.0), (' speed', 1.0), (' of', 1.0), (' a', 1.0), (' Formula', 1.0), (' ', 1.0), ('1', 1.0), (' car', 1.0), (' is', 1.0), (' ', 1.0), ('360', 1.0), (' km', 1.0), ('/h', 1.0), (' (', 1.0), ('220', 1.0), (' mph', 1.0), (').', 1.0), (' The', 1.0), (' fastest', 1.0), (' speed', 1.0), (' ever', 1.0), (' recorded', 1.0), (' in', 1.0), (' a', 1.0)]</t>
         </is>
       </c>
       <c r="M73" t="n">
@@ -4340,24 +4340,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Formula 1 cars are the fastest road-racing cars in the world.</t>
+          <t>The top speed of a Formula 1 car is 360 km/h (220 mph). The fastest speed ever recorded in a</t>
         </is>
       </c>
       <c r="H74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
-        <v>0.9117</v>
+        <v>0.9727</v>
       </c>
       <c r="K74" t="n">
-        <v>0.6930999755859375</v>
+        <v>0.3465999960899353</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>[0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' The', 0.5), (' top', 1.0), (' speed', 1.0), (' of', 1.0), (' a', 1.0), (' Formula', 1.0), (' ', 1.0), ('1', 1.0), (' car', 1.0), (' is', 1.0), (' ', 1.0), ('360', 1.0), (' km', 1.0), ('/h', 1.0), (' (', 1.0), ('220', 1.0), (' mph', 1.0), (').', 1.0), (' The', 1.0), (' fastest', 1.0), (' speed', 1.0), (' ever', 1.0), (' recorded', 1.0), (' in', 1.0), (' a', 1.0)]</t>
         </is>
       </c>
       <c r="M74" t="n">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Formula 1 cars are the fastest road racing cars in the world.</t>
+          <t>Formula 1 cars are the fastest road-racing cars in the world. They are designed to go around a track as fast</t>
         </is>
       </c>
       <c r="H75" t="b">
@@ -4403,14 +4403,14 @@
         <v>0.25</v>
       </c>
       <c r="J75" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="K75" t="n">
         <v>0.6930999755859375</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>[0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Formula', 0.5), (' ', 1.0), ('1', 1.0), (' cars', 1.0), (' are', 1.0), (' the', 1.0), (' fastest', 1.0), (' road', 1.0), ('-r', 0.5), ('acing', 1.0), (' cars', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' They', 1.0), (' are', 1.0), (' designed', 1.0), (' to', 1.0), (' go', 1.0), (' around', 1.0), (' a', 1.0), (' track', 1.0), (' as', 1.0), (' fast', 1.0)]</t>
         </is>
       </c>
       <c r="M75" t="n">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Formula 1 cars are the fastest road-racing cars in the world.</t>
+          <t>Formula 1 cars are the fastest road-racing cars in the world. They are designed to go around a track as fast</t>
         </is>
       </c>
       <c r="H76" t="b">
@@ -4456,14 +4456,14 @@
         <v>0.25</v>
       </c>
       <c r="J76" t="n">
-        <v>0.9117</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="K76" t="n">
         <v>0.6930999755859375</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>[0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Formula', 0.5), (' ', 1.0), ('1', 1.0), (' cars', 1.0), (' are', 1.0), (' the', 1.0), (' fastest', 1.0), (' road', 1.0), ('-r', 0.5), ('acing', 1.0), (' cars', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' They', 1.0), (' are', 1.0), (' designed', 1.0), (' to', 1.0), (' go', 1.0), (' around', 1.0), (' a', 1.0), (' track', 1.0), (' as', 1.0), (' fast', 1.0)]</t>
         </is>
       </c>
       <c r="M76" t="n">
@@ -4499,24 +4499,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in, the type of customers you have, and the type</t>
         </is>
       </c>
       <c r="H77" t="b">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7773</v>
+        <v>0.2531</v>
       </c>
       <c r="J77" t="n">
-        <v>0.9195</v>
+        <v>0.9465</v>
       </c>
       <c r="K77" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.8216000199317932</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' customers', 0.6514), (' you', 1.0), (' have', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' type', 1.0)]</t>
         </is>
       </c>
       <c r="M77" t="n">
@@ -4552,24 +4552,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in, the type of customers you have, and the type</t>
         </is>
       </c>
       <c r="H78" t="b">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7773</v>
+        <v>0.2531</v>
       </c>
       <c r="J78" t="n">
-        <v>0.9195</v>
+        <v>0.9465</v>
       </c>
       <c r="K78" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.8216000199317932</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' customers', 0.6514), (' you', 1.0), (' have', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' type', 1.0)]</t>
         </is>
       </c>
       <c r="M78" t="n">
@@ -4605,24 +4605,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But you need to be careful. The reason is that the IRS has a very strict definition of what</t>
         </is>
       </c>
       <c r="H79" t="b">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7773</v>
+        <v>0.0216</v>
       </c>
       <c r="J79" t="n">
-        <v>0.9195</v>
+        <v>0.8578</v>
       </c>
       <c r="K79" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.570000052452087</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' you', 0.5), (' need', 0.5), (' to', 1.0), (' be', 1.0), (' careful', 1.0), ('.', 1.0), (' The', 0.5), (' reason', 1.0), (' is', 1.0), (' that', 1.0), (' the', 1.0), (' IRS', 1.0), (' has', 1.0), (' a', 1.0), (' very', 0.7773), (' strict', 1.0), (' definition', 1.0), (' of', 1.0), (' what', 1.0)]</t>
         </is>
       </c>
       <c r="M79" t="n">
@@ -4658,24 +4658,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H80" t="b">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J80" t="n">
-        <v>0.9195</v>
+        <v>0.9629</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M80" t="n">
@@ -4711,24 +4711,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H81" t="b">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.2227</v>
+        <v>0.3886</v>
       </c>
       <c r="J81" t="n">
-        <v>0.7405</v>
+        <v>0.9629</v>
       </c>
       <c r="K81" t="n">
-        <v>0.3345000147819519</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M81" t="n">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>The main ingredient of a Caesar salad is romaine lettuce.</t>
+          <t>The main ingredient of a Caesar salad is romaine lettuce. The dressing is</t>
         </is>
       </c>
       <c r="H82" t="b">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' The', 1.0), (' main', 1.0), (' ingredient', 1.0), (' of', 1.0), (' a', 1.0), (' Caesar', 1.0), (' salad', 1.0), (' is', 1.0), (' rom', 1.0), ('aine', 1.0), (' lettuce', 1.0), ('.', 1.0), (' The', 1.0), (' dressing', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="M82" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>The main ingredient of a Caesar salad is romaine lettuce.</t>
+          <t>The main ingredient of a Caesar salad is romaine lettuce. The dressing is</t>
         </is>
       </c>
       <c r="H83" t="b">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' The', 1.0), (' main', 1.0), (' ingredient', 1.0), (' of', 1.0), (' a', 1.0), (' Caesar', 1.0), (' salad', 1.0), (' is', 1.0), (' rom', 1.0), ('aine', 1.0), (' lettuce', 1.0), ('.', 1.0), (' The', 1.0), (' dressing', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="M83" t="n">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>The main ingredient of a Caesar salad is romaine lettuce.</t>
+          <t>The main ingredient of a Caesar salad is romaine lettuce. The dressing is</t>
         </is>
       </c>
       <c r="H84" t="b">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' The', 1.0), (' main', 1.0), (' ingredient', 1.0), (' of', 1.0), (' a', 1.0), (' Caesar', 1.0), (' salad', 1.0), (' is', 1.0), (' rom', 1.0), ('aine', 1.0), (' lettuce', 1.0), ('.', 1.0), (' The', 1.0), (' dressing', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="M84" t="n">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>The main ingredient of a Caesar salad is romaine lettuce.</t>
+          <t>The main ingredient of a Caesar salad is romaine lettuce. The dressing is</t>
         </is>
       </c>
       <c r="H85" t="b">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' The', 1.0), (' main', 1.0), (' ingredient', 1.0), (' of', 1.0), (' a', 1.0), (' Caesar', 1.0), (' salad', 1.0), (' is', 1.0), (' rom', 1.0), ('aine', 1.0), (' lettuce', 1.0), ('.', 1.0), (' The', 1.0), (' dressing', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="M85" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>The main ingredient of a Caesar salad is romaine lettuce.</t>
+          <t>The main ingredient of a Caesar salad is romaine lettuce. The dressing is</t>
         </is>
       </c>
       <c r="H86" t="b">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' The', 1.0), (' main', 1.0), (' ingredient', 1.0), (' of', 1.0), (' a', 1.0), (' Caesar', 1.0), (' salad', 1.0), (' is', 1.0), (' rom', 1.0), ('aine', 1.0), (' lettuce', 1.0), ('.', 1.0), (' The', 1.0), (' dressing', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="M86" t="n">
@@ -5029,24 +5029,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H87" t="b">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J87" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M87" t="n">
@@ -5082,24 +5082,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in,</t>
         </is>
       </c>
       <c r="H88" t="b">
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J88" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K88" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M88" t="n">
@@ -5135,24 +5135,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But you should be aware of the risks involved.</t>
         </is>
       </c>
       <c r="H89" t="b">
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7773</v>
+        <v>0.0557</v>
       </c>
       <c r="J89" t="n">
-        <v>0.9195</v>
+        <v>0.8249</v>
       </c>
       <c r="K89" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.027600049972534</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' you', 0.5), (' should', 0.5), (' be', 1.0), (' aware', 1.0), (' of', 1.0), (' the', 1.0), (' risks', 1.0), (' involved', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="M89" t="n">
@@ -5188,24 +5188,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in,</t>
         </is>
       </c>
       <c r="H90" t="b">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J90" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K90" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M90" t="n">
@@ -5241,24 +5241,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in,</t>
         </is>
       </c>
       <c r="H91" t="b">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J91" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K91" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M91" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>The main ingredient of a Caesar salad is romaine lettuce.</t>
+          <t>The main ingredient of a Caesar salad is romaine lettuce. The dressing is made with anchovies, garlic, lemon juice,</t>
         </is>
       </c>
       <c r="H92" t="b">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' The', 1.0), (' main', 1.0), (' ingredient', 1.0), (' of', 1.0), (' a', 1.0), (' Caesar', 1.0), (' salad', 1.0), (' is', 1.0), (' rom', 1.0), ('aine', 1.0), (' lettuce', 1.0), ('.', 1.0), (' The', 1.0), (' dressing', 1.0), (' is', 1.0), (' made', 1.0), (' with', 1.0), (' anch', 1.0), ('ovies', 1.0), (',', 1.0), (' garlic', 1.0), (',', 1.0), (' lemon', 1.0), (' juice', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M92" t="n">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>The main ingredient of a Caesar salad is romaine lettuce.</t>
+          <t>The main ingredient of a Caesar salad is romaine lettuce. The dressing is made with anchovies, garlic, lemon juice,</t>
         </is>
       </c>
       <c r="H93" t="b">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' The', 1.0), (' main', 1.0), (' ingredient', 1.0), (' of', 1.0), (' a', 1.0), (' Caesar', 1.0), (' salad', 1.0), (' is', 1.0), (' rom', 1.0), ('aine', 1.0), (' lettuce', 1.0), ('.', 1.0), (' The', 1.0), (' dressing', 1.0), (' is', 1.0), (' made', 1.0), (' with', 1.0), (' anch', 1.0), ('ovies', 1.0), (',', 1.0), (' garlic', 1.0), (',', 1.0), (' lemon', 1.0), (' juice', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M93" t="n">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>The main ingredient of a Caesar salad is romaine lettuce.</t>
+          <t>The main ingredient of a Caesar salad is romaine lettuce. The dressing is made with anchovies, garlic, lemon juice,</t>
         </is>
       </c>
       <c r="H94" t="b">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' The', 1.0), (' main', 1.0), (' ingredient', 1.0), (' of', 1.0), (' a', 1.0), (' Caesar', 1.0), (' salad', 1.0), (' is', 1.0), (' rom', 1.0), ('aine', 1.0), (' lettuce', 1.0), ('.', 1.0), (' The', 1.0), (' dressing', 1.0), (' is', 1.0), (' made', 1.0), (' with', 1.0), (' anch', 1.0), ('ovies', 1.0), (',', 1.0), (' garlic', 1.0), (',', 1.0), (' lemon', 1.0), (' juice', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M94" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>The main ingredient of a Caesar salad is romaine lettuce.</t>
+          <t>The main ingredient of a Caesar salad is romaine lettuce. The dressing is made with anchovies, garlic, lemon juice,</t>
         </is>
       </c>
       <c r="H95" t="b">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' The', 1.0), (' main', 1.0), (' ingredient', 1.0), (' of', 1.0), (' a', 1.0), (' Caesar', 1.0), (' salad', 1.0), (' is', 1.0), (' rom', 1.0), ('aine', 1.0), (' lettuce', 1.0), ('.', 1.0), (' The', 1.0), (' dressing', 1.0), (' is', 1.0), (' made', 1.0), (' with', 1.0), (' anch', 1.0), ('ovies', 1.0), (',', 1.0), (' garlic', 1.0), (',', 1.0), (' lemon', 1.0), (' juice', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M95" t="n">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>The main ingredient of a Caesar salad is romaine lettuce.</t>
+          <t>The main ingredient of a Caesar salad is romaine lettuce. The dressing is made with anchovies, garlic, lemon juice,</t>
         </is>
       </c>
       <c r="H96" t="b">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' The', 1.0), (' main', 1.0), (' ingredient', 1.0), (' of', 1.0), (' a', 1.0), (' Caesar', 1.0), (' salad', 1.0), (' is', 1.0), (' rom', 1.0), ('aine', 1.0), (' lettuce', 1.0), ('.', 1.0), (' The', 1.0), (' dressing', 1.0), (' is', 1.0), (' made', 1.0), (' with', 1.0), (' anch', 1.0), ('ovies', 1.0), (',', 1.0), (' garlic', 1.0), (',', 1.0), (' lemon', 1.0), (' juice', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M96" t="n">
@@ -5559,24 +5559,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H97" t="b">
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J97" t="n">
-        <v>0.9195</v>
+        <v>0.9629</v>
       </c>
       <c r="K97" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M97" t="n">
@@ -5612,24 +5612,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H98" t="b">
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J98" t="n">
-        <v>0.9195</v>
+        <v>0.9629</v>
       </c>
       <c r="K98" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M98" t="n">
@@ -5665,24 +5665,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H99" t="b">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2227</v>
+        <v>0.3886</v>
       </c>
       <c r="J99" t="n">
-        <v>0.7405</v>
+        <v>0.9629</v>
       </c>
       <c r="K99" t="n">
-        <v>0.3345000147819519</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M99" t="n">
@@ -5718,24 +5718,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>it depends. The answer depends on the type of business you are in, the type of customers you have, and the type</t>
         </is>
       </c>
       <c r="H100" t="b">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2227</v>
+        <v>0.2531</v>
       </c>
       <c r="J100" t="n">
-        <v>0.7405</v>
+        <v>0.9465</v>
       </c>
       <c r="K100" t="n">
-        <v>0.3345000147819519</v>
+        <v>0.8216000199317932</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' customers', 0.6514), (' you', 1.0), (' have', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' type', 1.0)]</t>
         </is>
       </c>
       <c r="M100" t="n">
@@ -5771,24 +5771,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H101" t="b">
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J101" t="n">
-        <v>0.9195</v>
+        <v>0.9629</v>
       </c>
       <c r="K101" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M101" t="n">
@@ -5824,24 +5824,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Paris is the capital city of France.</t>
+          <t>Paris is the capital city of France. The city is located in the north</t>
         </is>
       </c>
       <c r="H102" t="b">
         <v>1</v>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>0.2227</v>
       </c>
       <c r="J102" t="n">
-        <v>1</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="K102" t="n">
-        <v>-0</v>
+        <v>0.3345000147819519</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' The', 0.2227), (' city', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0)]</t>
         </is>
       </c>
       <c r="M102" t="n">
@@ -5877,24 +5877,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Paris is the capital city of France.</t>
+          <t>Paris is the capital city of France. Paris is the capital city of France</t>
         </is>
       </c>
       <c r="H103" t="b">
         <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>0.7773</v>
       </c>
       <c r="J103" t="n">
-        <v>1</v>
+        <v>0.9833</v>
       </c>
       <c r="K103" t="n">
-        <v>-0</v>
+        <v>0.1958000063896179</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' Paris', 0.7773), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0)]</t>
         </is>
       </c>
       <c r="M103" t="n">
@@ -5930,24 +5930,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Paris is the capital city of France.</t>
+          <t>Paris is the capital city of France. Paris is the capital city of France</t>
         </is>
       </c>
       <c r="H104" t="b">
         <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>0.7773</v>
       </c>
       <c r="J104" t="n">
-        <v>1</v>
+        <v>0.9833</v>
       </c>
       <c r="K104" t="n">
-        <v>-0</v>
+        <v>0.1958000063896179</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' Paris', 0.7773), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0)]</t>
         </is>
       </c>
       <c r="M104" t="n">
@@ -5983,24 +5983,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Paris is the capital city of France.</t>
+          <t>Paris is the capital city of France. Paris is the capital city of France</t>
         </is>
       </c>
       <c r="H105" t="b">
         <v>1</v>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>0.7773</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>0.9833</v>
       </c>
       <c r="K105" t="n">
-        <v>-0</v>
+        <v>0.1958000063896179</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' Paris', 0.7773), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0)]</t>
         </is>
       </c>
       <c r="M105" t="n">
@@ -6036,24 +6036,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Paris is the capital city of France.</t>
+          <t>Paris is the capital city of France. Paris is the capital city of France</t>
         </is>
       </c>
       <c r="H106" t="b">
         <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>0.7773</v>
       </c>
       <c r="J106" t="n">
-        <v>1</v>
+        <v>0.9833</v>
       </c>
       <c r="K106" t="n">
-        <v>-0</v>
+        <v>0.1958000063896179</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' Paris', 0.7773), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0)]</t>
         </is>
       </c>
       <c r="M106" t="n">
@@ -6089,24 +6089,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in,</t>
         </is>
       </c>
       <c r="H107" t="b">
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J107" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K107" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M107" t="n">
@@ -6142,24 +6142,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But it’s not as simple as it sounds.</t>
         </is>
       </c>
       <c r="H108" t="b">
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7773</v>
+        <v>0.0557</v>
       </c>
       <c r="J108" t="n">
-        <v>0.9195</v>
+        <v>0.8249</v>
       </c>
       <c r="K108" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.027600049972534</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' it', 0.5), ('’s', 1.0), (' not', 1.0), (' as', 1.0), (' simple', 0.5), (' as', 1.0), (' it', 1.0), (' sounds', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="M108" t="n">
@@ -6195,24 +6195,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But you should be aware of the risks involved.</t>
         </is>
       </c>
       <c r="H109" t="b">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>0.7773</v>
+        <v>0.0557</v>
       </c>
       <c r="J109" t="n">
-        <v>0.9195</v>
+        <v>0.8249</v>
       </c>
       <c r="K109" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.027600049972534</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' you', 0.5), (' should', 0.5), (' be', 1.0), (' aware', 1.0), (' of', 1.0), (' the', 1.0), (' risks', 1.0), (' involved', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="M109" t="n">
@@ -6248,24 +6248,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in,</t>
         </is>
       </c>
       <c r="H110" t="b">
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J110" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K110" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M110" t="n">
@@ -6301,24 +6301,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H111" t="b">
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J111" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K111" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M111" t="n">
@@ -6354,24 +6354,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Paris is the capital city of France.</t>
+          <t>Paris is the capital city of France. Paris is the capital city of France. Paris is the capital city of France. Paris</t>
         </is>
       </c>
       <c r="H112" t="b">
         <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>0.7773</v>
       </c>
       <c r="J112" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="K112" t="n">
-        <v>-0</v>
+        <v>0.1958000063896179</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' Paris', 0.7773), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="M112" t="n">
@@ -6407,24 +6407,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Paris is the capital city of France.</t>
+          <t>Paris is the capital city of France. The city is located in the north-central part of the country. Paris is the largest</t>
         </is>
       </c>
       <c r="H113" t="b">
         <v>1</v>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>0.2227</v>
       </c>
       <c r="J113" t="n">
-        <v>1</v>
+        <v>0.9417</v>
       </c>
       <c r="K113" t="n">
-        <v>-0</v>
+        <v>0.3345000147819519</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' The', 0.2227), (' city', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' north', 1.0), ('-central', 1.0), (' part', 1.0), (' of', 1.0), (' the', 1.0), (' country', 1.0), ('.', 1.0), (' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0)]</t>
         </is>
       </c>
       <c r="M113" t="n">
@@ -6460,24 +6460,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Paris is the capital city of France.</t>
+          <t>Paris is the capital city of France. Paris is the capital city of France. Paris is the capital city of France. Paris</t>
         </is>
       </c>
       <c r="H114" t="b">
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>0.7773</v>
       </c>
       <c r="J114" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="K114" t="n">
-        <v>-0</v>
+        <v>0.1958000063896179</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' Paris', 0.7773), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="M114" t="n">
@@ -6513,24 +6513,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Paris is the capital city of France.</t>
+          <t>Paris is the capital city of France. Paris is the capital city of France. Paris is the capital city of France. Paris</t>
         </is>
       </c>
       <c r="H115" t="b">
         <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>0.7773</v>
       </c>
       <c r="J115" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="K115" t="n">
-        <v>-0</v>
+        <v>0.1958000063896179</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' Paris', 0.7773), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="M115" t="n">
@@ -6566,24 +6566,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Paris is the capital city of France.</t>
+          <t>Paris is the capital city of France. Paris is the capital city of France. Paris is the capital city of France. Paris</t>
         </is>
       </c>
       <c r="H116" t="b">
         <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0.7773</v>
       </c>
       <c r="J116" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="K116" t="n">
-        <v>-0</v>
+        <v>0.1958000063896179</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' Paris', 0.7773), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' France', 1.0), ('.', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="M116" t="n">
@@ -6619,24 +6619,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H117" t="b">
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J117" t="n">
-        <v>0.9195</v>
+        <v>0.9629</v>
       </c>
       <c r="K117" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M117" t="n">
@@ -6672,24 +6672,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in, the type of customers you have, and the type</t>
         </is>
       </c>
       <c r="H118" t="b">
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7773</v>
+        <v>0.2531</v>
       </c>
       <c r="J118" t="n">
-        <v>0.9195</v>
+        <v>0.9465</v>
       </c>
       <c r="K118" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.8216000199317932</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' customers', 0.6514), (' you', 1.0), (' have', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' type', 1.0)]</t>
         </is>
       </c>
       <c r="M118" t="n">
@@ -6725,24 +6725,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H119" t="b">
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J119" t="n">
-        <v>0.9195</v>
+        <v>0.9629</v>
       </c>
       <c r="K119" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M119" t="n">
@@ -6778,24 +6778,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H120" t="b">
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J120" t="n">
-        <v>0.9195</v>
+        <v>0.9629</v>
       </c>
       <c r="K120" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M120" t="n">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>yes, you can. But you need to be careful. The reason is that the IRS has a very strict definition of what</t>
         </is>
       </c>
       <c r="H121" t="b">
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>0.2227</v>
+        <v>0.0216</v>
       </c>
       <c r="J121" t="n">
-        <v>0.7405</v>
+        <v>0.8578</v>
       </c>
       <c r="K121" t="n">
-        <v>0.3345000147819519</v>
+        <v>1.570000052452087</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' you', 0.5), (' need', 0.5), (' to', 1.0), (' be', 1.0), (' careful', 1.0), ('.', 1.0), (' The', 0.5), (' reason', 1.0), (' is', 1.0), (' that', 1.0), (' the', 1.0), (' IRS', 1.0), (' has', 1.0), (' a', 1.0), (' very', 0.7773), (' strict', 1.0), (' definition', 1.0), (' of', 1.0), (' what', 1.0)]</t>
         </is>
       </c>
       <c r="M121" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alexander Fleming discovered penicillin in 1928.</t>
+          <t>Alexander Fleming discovered penicillin in 1928. He was a Scottish</t>
         </is>
       </c>
       <c r="H122" t="b">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alexander', 1.0), (' Fleming', 1.0), (' discovered', 1.0), (' pen', 1.0), ('ic', 1.0), ('illin', 1.0), (' in', 1.0), (' ', 1.0), ('192', 1.0), ('8', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' a', 1.0), (' Scottish', 1.0)]</t>
         </is>
       </c>
       <c r="M122" t="n">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alexander Fleming discovered penicillin in 1928.</t>
+          <t>Alexander Fleming discovered penicillin in 1928. He was a Scottish</t>
         </is>
       </c>
       <c r="H123" t="b">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alexander', 1.0), (' Fleming', 1.0), (' discovered', 1.0), (' pen', 1.0), ('ic', 1.0), ('illin', 1.0), (' in', 1.0), (' ', 1.0), ('192', 1.0), ('8', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' a', 1.0), (' Scottish', 1.0)]</t>
         </is>
       </c>
       <c r="M123" t="n">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alexander Fleming discovered penicillin in 1928.</t>
+          <t>Alexander Fleming discovered penicillin in 1928. He was a Scottish</t>
         </is>
       </c>
       <c r="H124" t="b">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alexander', 1.0), (' Fleming', 1.0), (' discovered', 1.0), (' pen', 1.0), ('ic', 1.0), ('illin', 1.0), (' in', 1.0), (' ', 1.0), ('192', 1.0), ('8', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' a', 1.0), (' Scottish', 1.0)]</t>
         </is>
       </c>
       <c r="M124" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alexander Fleming discovered penicillin in 1928.</t>
+          <t>Alexander Fleming discovered penicillin in 1928. He was a Scottish</t>
         </is>
       </c>
       <c r="H125" t="b">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alexander', 1.0), (' Fleming', 1.0), (' discovered', 1.0), (' pen', 1.0), ('ic', 1.0), ('illin', 1.0), (' in', 1.0), (' ', 1.0), ('192', 1.0), ('8', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' a', 1.0), (' Scottish', 1.0)]</t>
         </is>
       </c>
       <c r="M125" t="n">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alexander Fleming discovered penicillin in 1928.</t>
+          <t>Alexander Fleming discovered penicillin in 1928. He was a Scottish</t>
         </is>
       </c>
       <c r="H126" t="b">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alexander', 1.0), (' Fleming', 1.0), (' discovered', 1.0), (' pen', 1.0), ('ic', 1.0), ('illin', 1.0), (' in', 1.0), (' ', 1.0), ('192', 1.0), ('8', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' a', 1.0), (' Scottish', 1.0)]</t>
         </is>
       </c>
       <c r="M126" t="n">
@@ -7149,24 +7149,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in,</t>
         </is>
       </c>
       <c r="H127" t="b">
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J127" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K127" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M127" t="n">
@@ -7202,24 +7202,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H128" t="b">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2227</v>
+        <v>0.3886</v>
       </c>
       <c r="J128" t="n">
-        <v>0.7405</v>
+        <v>0.9389</v>
       </c>
       <c r="K128" t="n">
-        <v>0.3345000147819519</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M128" t="n">
@@ -7255,24 +7255,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H129" t="b">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J129" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K129" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M129" t="n">
@@ -7308,24 +7308,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in,</t>
         </is>
       </c>
       <c r="H130" t="b">
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J130" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K130" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M130" t="n">
@@ -7361,24 +7361,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But you should be aware of the risks involved.</t>
         </is>
       </c>
       <c r="H131" t="b">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>0.7773</v>
+        <v>0.0557</v>
       </c>
       <c r="J131" t="n">
-        <v>0.9195</v>
+        <v>0.8249</v>
       </c>
       <c r="K131" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.027600049972534</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' you', 0.5), (' should', 0.5), (' be', 1.0), (' aware', 1.0), (' of', 1.0), (' the', 1.0), (' risks', 1.0), (' involved', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="M131" t="n">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alexander Fleming discovered penicillin in 1928.</t>
+          <t>Alexander Fleming discovered penicillin in 1928. He was a Scottish biologist, pharmacologist, and botanist.</t>
         </is>
       </c>
       <c r="H132" t="b">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alexander', 1.0), (' Fleming', 1.0), (' discovered', 1.0), (' pen', 1.0), ('ic', 1.0), ('illin', 1.0), (' in', 1.0), (' ', 1.0), ('192', 1.0), ('8', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' a', 1.0), (' Scottish', 1.0), (' biologist', 1.0), (',', 1.0), (' pharmac', 1.0), ('ologist', 1.0), (',', 1.0), (' and', 1.0), (' bot', 1.0), ('an', 1.0), ('ist', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="M132" t="n">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alexander Fleming discovered penicillin in 1928.</t>
+          <t>Alexander Fleming discovered penicillin in 1928. He was a Scottish biologist, pharmacologist, and botanist.</t>
         </is>
       </c>
       <c r="H133" t="b">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alexander', 1.0), (' Fleming', 1.0), (' discovered', 1.0), (' pen', 1.0), ('ic', 1.0), ('illin', 1.0), (' in', 1.0), (' ', 1.0), ('192', 1.0), ('8', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' a', 1.0), (' Scottish', 1.0), (' biologist', 1.0), (',', 1.0), (' pharmac', 1.0), ('ologist', 1.0), (',', 1.0), (' and', 1.0), (' bot', 1.0), ('an', 1.0), ('ist', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="M133" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alexander Fleming discovered penicillin in 1928.</t>
+          <t>Alexander Fleming discovered penicillin in 1928. He was a Scottish biologist, pharmacologist, and botanist.</t>
         </is>
       </c>
       <c r="H134" t="b">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alexander', 1.0), (' Fleming', 1.0), (' discovered', 1.0), (' pen', 1.0), ('ic', 1.0), ('illin', 1.0), (' in', 1.0), (' ', 1.0), ('192', 1.0), ('8', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' a', 1.0), (' Scottish', 1.0), (' biologist', 1.0), (',', 1.0), (' pharmac', 1.0), ('ologist', 1.0), (',', 1.0), (' and', 1.0), (' bot', 1.0), ('an', 1.0), ('ist', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="M134" t="n">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alexander Fleming discovered penicillin in 1928.</t>
+          <t>Alexander Fleming discovered penicillin in 1928. He was a Scottish biologist, pharmacologist, and botanist.</t>
         </is>
       </c>
       <c r="H135" t="b">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alexander', 1.0), (' Fleming', 1.0), (' discovered', 1.0), (' pen', 1.0), ('ic', 1.0), ('illin', 1.0), (' in', 1.0), (' ', 1.0), ('192', 1.0), ('8', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' a', 1.0), (' Scottish', 1.0), (' biologist', 1.0), (',', 1.0), (' pharmac', 1.0), ('ologist', 1.0), (',', 1.0), (' and', 1.0), (' bot', 1.0), ('an', 1.0), ('ist', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="M135" t="n">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alexander Fleming discovered penicillin in 1928.</t>
+          <t>Alexander Fleming discovered penicillin in 1928. He was a Scottish biologist, pharmacologist, and botanist.</t>
         </is>
       </c>
       <c r="H136" t="b">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Alexander', 1.0), (' Fleming', 1.0), (' discovered', 1.0), (' pen', 1.0), ('ic', 1.0), ('illin', 1.0), (' in', 1.0), (' ', 1.0), ('192', 1.0), ('8', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' a', 1.0), (' Scottish', 1.0), (' biologist', 1.0), (',', 1.0), (' pharmac', 1.0), ('ologist', 1.0), (',', 1.0), (' and', 1.0), (' bot', 1.0), ('an', 1.0), ('ist', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="M136" t="n">
@@ -7679,24 +7679,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But it’s not as simple as it sounds. There are a few things you need to know before</t>
         </is>
       </c>
       <c r="H137" t="b">
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7773</v>
+        <v>0.0557</v>
       </c>
       <c r="J137" t="n">
-        <v>0.9195</v>
+        <v>0.8909</v>
       </c>
       <c r="K137" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.027600049972534</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' it', 0.5), ('’s', 1.0), (' not', 1.0), (' as', 1.0), (' simple', 0.5), (' as', 1.0), (' it', 1.0), (' sounds', 1.0), ('.', 1.0), (' There', 1.0), (' are', 1.0), (' a', 1.0), (' few', 1.0), (' things', 1.0), (' you', 1.0), (' need', 1.0), (' to', 1.0), (' know', 1.0), (' before', 1.0)]</t>
         </is>
       </c>
       <c r="M137" t="n">
@@ -7732,24 +7732,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in, the type of customers you have, and the type</t>
         </is>
       </c>
       <c r="H138" t="b">
         <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>0.7773</v>
+        <v>0.2531</v>
       </c>
       <c r="J138" t="n">
-        <v>0.9195</v>
+        <v>0.9465</v>
       </c>
       <c r="K138" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.8216000199317932</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' customers', 0.6514), (' you', 1.0), (' have', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' type', 1.0)]</t>
         </is>
       </c>
       <c r="M138" t="n">
@@ -7785,24 +7785,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in, the type of customers you have, and the type</t>
         </is>
       </c>
       <c r="H139" t="b">
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>0.7773</v>
+        <v>0.2531</v>
       </c>
       <c r="J139" t="n">
-        <v>0.9195</v>
+        <v>0.9465</v>
       </c>
       <c r="K139" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.8216000199317932</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' customers', 0.6514), (' you', 1.0), (' have', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' type', 1.0)]</t>
         </is>
       </c>
       <c r="M139" t="n">
@@ -7838,24 +7838,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But it’s not as simple as it sounds. There are a few things you need to know before</t>
         </is>
       </c>
       <c r="H140" t="b">
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>0.7773</v>
+        <v>0.0557</v>
       </c>
       <c r="J140" t="n">
-        <v>0.9195</v>
+        <v>0.8909</v>
       </c>
       <c r="K140" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.027600049972534</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' it', 0.5), ('’s', 1.0), (' not', 1.0), (' as', 1.0), (' simple', 0.5), (' as', 1.0), (' it', 1.0), (' sounds', 1.0), ('.', 1.0), (' There', 1.0), (' are', 1.0), (' a', 1.0), (' few', 1.0), (' things', 1.0), (' you', 1.0), (' need', 1.0), (' to', 1.0), (' know', 1.0), (' before', 1.0)]</t>
         </is>
       </c>
       <c r="M140" t="n">
@@ -7891,24 +7891,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H141" t="b">
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J141" t="n">
-        <v>0.9195</v>
+        <v>0.9629</v>
       </c>
       <c r="K141" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M141" t="n">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil.</t>
+          <t>Portuguese is the official language of Brazil. It is spoken by 99%</t>
         </is>
       </c>
       <c r="H142" t="b">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0)]</t>
         </is>
       </c>
       <c r="M142" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil.</t>
+          <t>Portuguese is the official language of Brazil. It is spoken by 99%</t>
         </is>
       </c>
       <c r="H143" t="b">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0)]</t>
         </is>
       </c>
       <c r="M143" t="n">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil.</t>
+          <t>Portuguese is the official language of Brazil. It is spoken by 99%</t>
         </is>
       </c>
       <c r="H144" t="b">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0)]</t>
         </is>
       </c>
       <c r="M144" t="n">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil.</t>
+          <t>Portuguese is the official language of Brazil. It is spoken by 99%</t>
         </is>
       </c>
       <c r="H145" t="b">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0)]</t>
         </is>
       </c>
       <c r="M145" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil.</t>
+          <t>Portuguese is the official language of Brazil. It is spoken by 99%</t>
         </is>
       </c>
       <c r="H146" t="b">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0)]</t>
         </is>
       </c>
       <c r="M146" t="n">
@@ -8209,24 +8209,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But it’s not as easy as it sounds.</t>
         </is>
       </c>
       <c r="H147" t="b">
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7773</v>
+        <v>0.0557</v>
       </c>
       <c r="J147" t="n">
-        <v>0.9195</v>
+        <v>0.8249</v>
       </c>
       <c r="K147" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.027600049972534</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' it', 0.5), ('’s', 1.0), (' not', 1.0), (' as', 1.0), (' easy', 0.5), (' as', 1.0), (' it', 1.0), (' sounds', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="M147" t="n">
@@ -8262,24 +8262,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in,</t>
         </is>
       </c>
       <c r="H148" t="b">
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J148" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K148" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M148" t="n">
@@ -8315,24 +8315,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>it depends. The answer depends on the type of business you are in,</t>
         </is>
       </c>
       <c r="H149" t="b">
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2227</v>
+        <v>0.3886</v>
       </c>
       <c r="J149" t="n">
-        <v>0.7405</v>
+        <v>0.9389</v>
       </c>
       <c r="K149" t="n">
-        <v>0.3345000147819519</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M149" t="n">
@@ -8368,24 +8368,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in,</t>
         </is>
       </c>
       <c r="H150" t="b">
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J150" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K150" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M150" t="n">
@@ -8421,24 +8421,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H151" t="b">
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J151" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K151" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M151" t="n">
@@ -8474,24 +8474,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil.</t>
+          <t>Portuguese is the official language of Brazil. It is spoken by 99% of the population. The other 1% speak</t>
         </is>
       </c>
       <c r="H152" t="b">
         <v>1</v>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>0.3257</v>
       </c>
       <c r="J152" t="n">
-        <v>1</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="K152" t="n">
-        <v>-0</v>
+        <v>0.6258000135421753</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' The', 1.0), (' other', 0.6514), (' ', 0.5), ('1', 1.0), ('%', 1.0), (' speak', 1.0)]</t>
         </is>
       </c>
       <c r="M152" t="n">
@@ -8527,24 +8527,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil.</t>
+          <t>Portuguese is the official language of Brazil. It is spoken by 99% of the population. The other 1% speak</t>
         </is>
       </c>
       <c r="H153" t="b">
         <v>1</v>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>0.3257</v>
       </c>
       <c r="J153" t="n">
-        <v>1</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="K153" t="n">
-        <v>-0</v>
+        <v>0.6258000135421753</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' The', 1.0), (' other', 0.6514), (' ', 0.5), ('1', 1.0), ('%', 1.0), (' speak', 1.0)]</t>
         </is>
       </c>
       <c r="M153" t="n">
@@ -8580,24 +8580,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil.</t>
+          <t>Portuguese is the official language of Brazil. It is spoken by 99% of the population. The remaining 1% speak</t>
         </is>
       </c>
       <c r="H154" t="b">
         <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>0.3486</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>0.9587</v>
       </c>
       <c r="K154" t="n">
-        <v>-0</v>
+        <v>0.3673999905586243</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' The', 1.0), (' remaining', 0.3486), (' ', 1.0), ('1', 1.0), ('%', 1.0), (' speak', 1.0)]</t>
         </is>
       </c>
       <c r="M154" t="n">
@@ -8633,24 +8633,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil.</t>
+          <t>Portuguese is the official language of Brazil. It is spoken by 99% of the population. The remaining 1% speak</t>
         </is>
       </c>
       <c r="H155" t="b">
         <v>1</v>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>0.3486</v>
       </c>
       <c r="J155" t="n">
-        <v>1</v>
+        <v>0.9587</v>
       </c>
       <c r="K155" t="n">
-        <v>-0</v>
+        <v>0.3673999905586243</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' The', 1.0), (' remaining', 0.3486), (' ', 1.0), ('1', 1.0), ('%', 1.0), (' speak', 1.0)]</t>
         </is>
       </c>
       <c r="M155" t="n">
@@ -8686,24 +8686,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Portuguese is the official language of Brazil.</t>
+          <t>Portuguese is the official language of Brazil. It is spoken by 99% of the population. The remaining 1% speak</t>
         </is>
       </c>
       <c r="H156" t="b">
         <v>1</v>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>0.3486</v>
       </c>
       <c r="J156" t="n">
-        <v>1</v>
+        <v>0.9587</v>
       </c>
       <c r="K156" t="n">
-        <v>-0</v>
+        <v>0.3673999905586243</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>[1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('99', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' The', 1.0), (' remaining', 0.3486), (' ', 1.0), ('1', 1.0), ('%', 1.0), (' speak', 1.0)]</t>
         </is>
       </c>
       <c r="M156" t="n">
@@ -8739,24 +8739,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>it depends. The answer depends on the type of business you are in, the type of business you want to be in,</t>
         </is>
       </c>
       <c r="H157" t="b">
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2227</v>
+        <v>0.0678</v>
       </c>
       <c r="J157" t="n">
-        <v>0.7405</v>
+        <v>0.8979</v>
       </c>
       <c r="K157" t="n">
-        <v>0.3345000147819519</v>
+        <v>1.25629997253418</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 0.3486), (' you', 1.0), (' want', 0.5), (' to', 1.0), (' be', 1.0), (' in', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M157" t="n">
@@ -8792,24 +8792,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H158" t="b">
         <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J158" t="n">
-        <v>0.9195</v>
+        <v>0.9629</v>
       </c>
       <c r="K158" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M158" t="n">
@@ -8845,24 +8845,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But you should be aware of the risks involved. The first thing you should know is that the IRS</t>
         </is>
       </c>
       <c r="H159" t="b">
         <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>0.7773</v>
+        <v>0.0126</v>
       </c>
       <c r="J159" t="n">
-        <v>0.9195</v>
+        <v>0.8396</v>
       </c>
       <c r="K159" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.674200057983398</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' you', 0.5), (' should', 0.5), (' be', 1.0), (' aware', 1.0), (' of', 1.0), (' the', 1.0), (' risks', 1.0), (' involved', 1.0), ('.', 1.0), (' The', 0.3486), (' first', 1.0), (' thing', 1.0), (' you', 1.0), (' should', 1.0), (' know', 1.0), (' is', 1.0), (' that', 1.0), (' the', 0.6514), (' IRS', 1.0)]</t>
         </is>
       </c>
       <c r="M159" t="n">
@@ -8898,24 +8898,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But it’s not as easy as it sounds. You need to know what you’re doing and have</t>
         </is>
       </c>
       <c r="H160" t="b">
         <v>0</v>
       </c>
       <c r="I160" t="n">
-        <v>0.7773</v>
+        <v>0.0278</v>
       </c>
       <c r="J160" t="n">
-        <v>0.9195</v>
+        <v>0.8665</v>
       </c>
       <c r="K160" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.374199986457825</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' it', 0.5), ('’s', 1.0), (' not', 1.0), (' as', 1.0), (' easy', 0.5), (' as', 1.0), (' it', 1.0), (' sounds', 1.0), ('.', 1.0), (' You', 0.5), (' need', 1.0), (' to', 1.0), (' know', 1.0), (' what', 1.0), (' you', 1.0), ('’re', 1.0), (' doing', 1.0), (' and', 1.0), (' have', 1.0)]</t>
         </is>
       </c>
       <c r="M160" t="n">
@@ -8951,24 +8951,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But you need to be careful. The reason is that the IRS has a rule that says you can</t>
         </is>
       </c>
       <c r="H161" t="b">
         <v>0</v>
       </c>
       <c r="I161" t="n">
-        <v>0.7773</v>
+        <v>0.0062</v>
       </c>
       <c r="J161" t="n">
-        <v>0.9195</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="K161" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.708699941635132</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' you', 0.5), (' need', 0.5), (' to', 1.0), (' be', 1.0), (' careful', 1.0), ('.', 1.0), (' The', 0.5), (' reason', 1.0), (' is', 1.0), (' that', 1.0), (' the', 1.0), (' IRS', 1.0), (' has', 1.0), (' a', 1.0), (' rule', 0.2227), (' that', 1.0), (' says', 1.0), (' you', 1.0), (' can', 1.0)]</t>
         </is>
       </c>
       <c r="M161" t="n">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Curry powder is not a spice, but a blend of spices.</t>
+          <t>Curry is a blend of spices, not a single spice. The most common</t>
         </is>
       </c>
       <c r="H162" t="b">
@@ -9014,14 +9014,14 @@
         <v>0.5</v>
       </c>
       <c r="J162" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.9548</v>
       </c>
       <c r="K162" t="n">
         <v>0.3465999960899353</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>[1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Curry', 1.0), (' is', 0.5), (' a', 1.0), (' blend', 1.0), (' of', 1.0), (' spices', 1.0), (',', 1.0), (' not', 1.0), (' a', 1.0), (' single', 1.0), (' spice', 1.0), ('.', 1.0), (' The', 1.0), (' most', 1.0), (' common', 1.0)]</t>
         </is>
       </c>
       <c r="M162" t="n">
@@ -9057,24 +9057,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Curry is a blend of spices, not a single spice.</t>
+          <t>Curry powder is not a spice, but a blend of spices. The primary</t>
         </is>
       </c>
       <c r="H163" t="b">
         <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5</v>
+        <v>0.3257</v>
       </c>
       <c r="J163" t="n">
-        <v>0.9439</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="K163" t="n">
-        <v>0.3465999960899353</v>
+        <v>0.6258000135421753</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>[1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Curry', 1.0), (' powder', 0.5), (' is', 1.0), (' not', 1.0), (' a', 1.0), (' spice', 1.0), (',', 1.0), (' but', 1.0), (' a', 1.0), (' blend', 1.0), (' of', 1.0), (' spices', 1.0), ('.', 1.0), (' The', 1.0), (' primary', 0.6514)]</t>
         </is>
       </c>
       <c r="M163" t="n">
@@ -9110,24 +9110,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Curry is a blend of spices, not a single spice.</t>
+          <t>Curry powder is not a spice, but a blend of spices. The primary</t>
         </is>
       </c>
       <c r="H164" t="b">
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>0.3257</v>
       </c>
       <c r="J164" t="n">
-        <v>0.9439</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="K164" t="n">
-        <v>0.3465999960899353</v>
+        <v>0.6258000135421753</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>[1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Curry', 1.0), (' powder', 0.5), (' is', 1.0), (' not', 1.0), (' a', 1.0), (' spice', 1.0), (',', 1.0), (' but', 1.0), (' a', 1.0), (' blend', 1.0), (' of', 1.0), (' spices', 1.0), ('.', 1.0), (' The', 1.0), (' primary', 0.6514)]</t>
         </is>
       </c>
       <c r="M164" t="n">
@@ -9163,24 +9163,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Curry powder is not a spice, but a blend of spices.</t>
+          <t>Curry powder is not a spice, but a blend of spices. The primary</t>
         </is>
       </c>
       <c r="H165" t="b">
         <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5</v>
+        <v>0.3257</v>
       </c>
       <c r="J165" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="K165" t="n">
-        <v>0.3465999960899353</v>
+        <v>0.6258000135421753</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>[1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Curry', 1.0), (' powder', 0.5), (' is', 1.0), (' not', 1.0), (' a', 1.0), (' spice', 1.0), (',', 1.0), (' but', 1.0), (' a', 1.0), (' blend', 1.0), (' of', 1.0), (' spices', 1.0), ('.', 1.0), (' The', 1.0), (' primary', 0.6514)]</t>
         </is>
       </c>
       <c r="M165" t="n">
@@ -9216,24 +9216,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Curry is a blend of spices, not a single spice.</t>
+          <t>Curry powder is not a spice, but a blend of spices. The primary</t>
         </is>
       </c>
       <c r="H166" t="b">
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>0.3257</v>
       </c>
       <c r="J166" t="n">
-        <v>0.9439</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="K166" t="n">
-        <v>0.3465999960899353</v>
+        <v>0.6258000135421753</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>[1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Curry', 1.0), (' powder', 0.5), (' is', 1.0), (' not', 1.0), (' a', 1.0), (' spice', 1.0), (',', 1.0), (' but', 1.0), (' a', 1.0), (' blend', 1.0), (' of', 1.0), (' spices', 1.0), ('.', 1.0), (' The', 1.0), (' primary', 0.6514)]</t>
         </is>
       </c>
       <c r="M166" t="n">
@@ -9269,24 +9269,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H167" t="b">
         <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>0.2227</v>
+        <v>0.3886</v>
       </c>
       <c r="J167" t="n">
-        <v>0.7405</v>
+        <v>0.9389</v>
       </c>
       <c r="K167" t="n">
-        <v>0.3345000147819519</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M167" t="n">
@@ -9322,24 +9322,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H168" t="b">
         <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2227</v>
+        <v>0.3886</v>
       </c>
       <c r="J168" t="n">
-        <v>0.7405</v>
+        <v>0.9389</v>
       </c>
       <c r="K168" t="n">
-        <v>0.3345000147819519</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M168" t="n">
@@ -9375,24 +9375,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H169" t="b">
         <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J169" t="n">
-        <v>0.9195</v>
+        <v>0.9389</v>
       </c>
       <c r="K169" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="M169" t="n">
@@ -9428,24 +9428,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But you need to be careful. You need to</t>
         </is>
       </c>
       <c r="H170" t="b">
         <v>0</v>
       </c>
       <c r="I170" t="n">
-        <v>0.7773</v>
+        <v>0.0278</v>
       </c>
       <c r="J170" t="n">
-        <v>0.9195</v>
+        <v>0.7876</v>
       </c>
       <c r="K170" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.374199986457825</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' you', 0.5), (' need', 0.5), (' to', 1.0), (' be', 1.0), (' careful', 1.0), ('.', 1.0), (' You', 0.5), (' need', 1.0), (' to', 1.0)]</t>
         </is>
       </c>
       <c r="M170" t="n">
@@ -9481,24 +9481,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>yes, you can. But you should be aware of the risks involved.</t>
         </is>
       </c>
       <c r="H171" t="b">
         <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>0.7773</v>
+        <v>0.0557</v>
       </c>
       <c r="J171" t="n">
-        <v>0.9195</v>
+        <v>0.8249</v>
       </c>
       <c r="K171" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.027600049972534</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' you', 0.5), (' should', 0.5), (' be', 1.0), (' aware', 1.0), (' of', 1.0), (' the', 1.0), (' risks', 1.0), (' involved', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="M171" t="n">
@@ -9534,24 +9534,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Curry is a blend of spices, not a single spice.</t>
+          <t>Curry powder is not a spice, but a blend of spices. The primary spice used in curry is turmeric, which gives</t>
         </is>
       </c>
       <c r="H172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5</v>
+        <v>0.3257</v>
       </c>
       <c r="J172" t="n">
-        <v>0.9439</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="K172" t="n">
-        <v>0.3465999960899353</v>
+        <v>0.6258000135421753</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>[1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Curry', 1.0), (' powder', 0.5), (' is', 1.0), (' not', 1.0), (' a', 1.0), (' spice', 1.0), (',', 1.0), (' but', 1.0), (' a', 1.0), (' blend', 1.0), (' of', 1.0), (' spices', 1.0), ('.', 1.0), (' The', 1.0), (' primary', 0.6514), (' spice', 1.0), (' used', 1.0), (' in', 1.0), (' curry', 1.0), (' is', 1.0), (' tur', 1.0), ('meric', 1.0), (',', 1.0), (' which', 1.0), (' gives', 1.0)]</t>
         </is>
       </c>
       <c r="M172" t="n">
@@ -9587,24 +9587,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Curry is a blend of spices, not a single spice.</t>
+          <t>Curry powder is not a spice, but a blend of spices. The primary spice used in curry is turmeric, which gives</t>
         </is>
       </c>
       <c r="H173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5</v>
+        <v>0.3257</v>
       </c>
       <c r="J173" t="n">
-        <v>0.9439</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="K173" t="n">
-        <v>0.3465999960899353</v>
+        <v>0.6258000135421753</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>[1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Curry', 1.0), (' powder', 0.5), (' is', 1.0), (' not', 1.0), (' a', 1.0), (' spice', 1.0), (',', 1.0), (' but', 1.0), (' a', 1.0), (' blend', 1.0), (' of', 1.0), (' spices', 1.0), ('.', 1.0), (' The', 1.0), (' primary', 0.6514), (' spice', 1.0), (' used', 1.0), (' in', 1.0), (' curry', 1.0), (' is', 1.0), (' tur', 1.0), ('meric', 1.0), (',', 1.0), (' which', 1.0), (' gives', 1.0)]</t>
         </is>
       </c>
       <c r="M173" t="n">
@@ -9640,24 +9640,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Curry is a blend of spices, not a single spice.</t>
+          <t>Curry powder is not a spice, but a blend of spices. The primary spice used in curry is turmeric, which gives</t>
         </is>
       </c>
       <c r="H174" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5</v>
+        <v>0.3257</v>
       </c>
       <c r="J174" t="n">
-        <v>0.9439</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="K174" t="n">
-        <v>0.3465999960899353</v>
+        <v>0.6258000135421753</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>[1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Curry', 1.0), (' powder', 0.5), (' is', 1.0), (' not', 1.0), (' a', 1.0), (' spice', 1.0), (',', 1.0), (' but', 1.0), (' a', 1.0), (' blend', 1.0), (' of', 1.0), (' spices', 1.0), ('.', 1.0), (' The', 1.0), (' primary', 0.6514), (' spice', 1.0), (' used', 1.0), (' in', 1.0), (' curry', 1.0), (' is', 1.0), (' tur', 1.0), ('meric', 1.0), (',', 1.0), (' which', 1.0), (' gives', 1.0)]</t>
         </is>
       </c>
       <c r="M174" t="n">
@@ -9693,24 +9693,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Curry is a blend of spices, not a single spice.</t>
+          <t>Curry is a blend of spices, not a single spice. The most common spices used in curry are turmeric, cumin</t>
         </is>
       </c>
       <c r="H175" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I175" t="n">
         <v>0.5</v>
       </c>
       <c r="J175" t="n">
-        <v>0.9439</v>
+        <v>0.9727</v>
       </c>
       <c r="K175" t="n">
         <v>0.3465999960899353</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>[1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Curry', 1.0), (' is', 0.5), (' a', 1.0), (' blend', 1.0), (' of', 1.0), (' spices', 1.0), (',', 1.0), (' not', 1.0), (' a', 1.0), (' single', 1.0), (' spice', 1.0), ('.', 1.0), (' The', 1.0), (' most', 1.0), (' common', 1.0), (' spices', 1.0), (' used', 1.0), (' in', 1.0), (' curry', 1.0), (' are', 1.0), (' tur', 1.0), ('meric', 1.0), (',', 1.0), (' c', 1.0), ('umin', 1.0)]</t>
         </is>
       </c>
       <c r="M175" t="n">
@@ -9746,24 +9746,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Curry powder is not a spice, but a blend of spices.</t>
+          <t>Curry powder is not a spice, but a blend of spices. The primary spice used in curry is turmeric, which gives</t>
         </is>
       </c>
       <c r="H176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I176" t="n">
-        <v>0.5</v>
+        <v>0.3257</v>
       </c>
       <c r="J176" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="K176" t="n">
-        <v>0.3465999960899353</v>
+        <v>0.6258000135421753</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>[1.0, 0.5, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' Curry', 1.0), (' powder', 0.5), (' is', 1.0), (' not', 1.0), (' a', 1.0), (' spice', 1.0), (',', 1.0), (' but', 1.0), (' a', 1.0), (' blend', 1.0), (' of', 1.0), (' spices', 1.0), ('.', 1.0), (' The', 1.0), (' primary', 0.6514), (' spice', 1.0), (' used', 1.0), (' in', 1.0), (' curry', 1.0), (' is', 1.0), (' tur', 1.0), ('meric', 1.0), (',', 1.0), (' which', 1.0), (' gives', 1.0)]</t>
         </is>
       </c>
       <c r="M176" t="n">
@@ -9799,24 +9799,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H177" t="b">
         <v>0</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7773</v>
+        <v>0.3886</v>
       </c>
       <c r="J177" t="n">
-        <v>0.9195</v>
+        <v>0.9629</v>
       </c>
       <c r="K177" t="n">
-        <v>0.1958000063896179</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M177" t="n">
@@ -9852,24 +9852,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>it depends. The</t>
         </is>
       </c>
       <c r="H178" t="b">
         <v>0</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2227</v>
+        <v>0.3886</v>
       </c>
       <c r="J178" t="n">
-        <v>0.7405</v>
+        <v>0.9629</v>
       </c>
       <c r="K178" t="n">
-        <v>0.3345000147819519</v>
+        <v>0.5424000024795532</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
         </is>
       </c>
       <c r="M178" t="n">
@@ -9905,24 +9905,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>it depends. The answer depends on the type of business you are in, the type of customers you have, and the type</t>
         </is>
       </c>
       <c r="H179" t="b">
         <v>0</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2227</v>
+        <v>0.2531</v>
       </c>
       <c r="J179" t="n">
-        <v>0.7405</v>
+        <v>0.9465</v>
       </c>
       <c r="K179" t="n">
-        <v>0.3345000147819519</v>
+        <v>0.8216000199317932</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' customers', 0.6514), (' you', 1.0), (' have', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' type', 1.0)]</t>
         </is>
       </c>
       <c r="M179" t="n">
@@ -9958,24 +9958,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>yes, you can.</t>
+          <t>it depends. The answer depends on the type of business you are in, the type of customers you have, and the type</t>
         </is>
       </c>
       <c r="H180" t="b">
         <v>0</v>
       </c>
       <c r="I180" t="n">
-        <v>0.2227</v>
+        <v>0.2531</v>
       </c>
       <c r="J180" t="n">
-        <v>0.7405</v>
+        <v>0.9465</v>
       </c>
       <c r="K180" t="n">
-        <v>0.3345000147819519</v>
+        <v>0.8216000199317932</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>[0.2227, 1.0, 1.0, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' customers', 0.6514), (' you', 1.0), (' have', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' type', 1.0)]</t>
         </is>
       </c>
       <c r="M180" t="n">
@@ -10011,27 +10011,3214 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>it depends.</t>
+          <t>it depends. The answer depends on the type of business you are in, the type of business you want to be in,</t>
         </is>
       </c>
       <c r="H181" t="b">
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>0.7773</v>
+        <v>0.0678</v>
       </c>
       <c r="J181" t="n">
-        <v>0.9195</v>
+        <v>0.8979</v>
       </c>
       <c r="K181" t="n">
-        <v>0.1958000063896179</v>
+        <v>1.25629997253418</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>[0.7773, 1.0, 1.0]</t>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 0.3486), (' you', 1.0), (' want', 0.5), (' to', 1.0), (' be', 1.0), (' in', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="M181" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>15</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>William Shakespeare wrote the play 'Hamlet'. The play was written in</t>
+        </is>
+      </c>
+      <c r="H182" t="b">
+        <v>1</v>
+      </c>
+      <c r="I182" t="n">
+        <v>1</v>
+      </c>
+      <c r="J182" t="n">
+        <v>1</v>
+      </c>
+      <c r="K182" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>[(' William', 1.0), (' Shakespeare', 1.0), (' wrote', 1.0), (' the', 1.0), (' play', 1.0), (" '", 1.0), ('Ham', 1.0), ('let', 1.0), ("'.", 1.0), (' The', 1.0), (' play', 1.0), (' was', 1.0), (' written', 1.0), (' in', 1.0), (' ', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>15</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>William Shakespeare wrote the play 'Hamlet'. The play was written in</t>
+        </is>
+      </c>
+      <c r="H183" t="b">
+        <v>1</v>
+      </c>
+      <c r="I183" t="n">
+        <v>1</v>
+      </c>
+      <c r="J183" t="n">
+        <v>1</v>
+      </c>
+      <c r="K183" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>[(' William', 1.0), (' Shakespeare', 1.0), (' wrote', 1.0), (' the', 1.0), (' play', 1.0), (" '", 1.0), ('Ham', 1.0), ('let', 1.0), ("'.", 1.0), (' The', 1.0), (' play', 1.0), (' was', 1.0), (' written', 1.0), (' in', 1.0), (' ', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M183" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>15</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>William Shakespeare wrote the play 'Hamlet'. The play was written in</t>
+        </is>
+      </c>
+      <c r="H184" t="b">
+        <v>1</v>
+      </c>
+      <c r="I184" t="n">
+        <v>1</v>
+      </c>
+      <c r="J184" t="n">
+        <v>1</v>
+      </c>
+      <c r="K184" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>[(' William', 1.0), (' Shakespeare', 1.0), (' wrote', 1.0), (' the', 1.0), (' play', 1.0), (" '", 1.0), ('Ham', 1.0), ('let', 1.0), ("'.", 1.0), (' The', 1.0), (' play', 1.0), (' was', 1.0), (' written', 1.0), (' in', 1.0), (' ', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M184" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>15</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>William Shakespeare wrote the play 'Hamlet'. The play was written in</t>
+        </is>
+      </c>
+      <c r="H185" t="b">
+        <v>1</v>
+      </c>
+      <c r="I185" t="n">
+        <v>1</v>
+      </c>
+      <c r="J185" t="n">
+        <v>1</v>
+      </c>
+      <c r="K185" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>[(' William', 1.0), (' Shakespeare', 1.0), (' wrote', 1.0), (' the', 1.0), (' play', 1.0), (" '", 1.0), ('Ham', 1.0), ('let', 1.0), ("'.", 1.0), (' The', 1.0), (' play', 1.0), (' was', 1.0), (' written', 1.0), (' in', 1.0), (' ', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M185" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>15</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>William Shakespeare wrote the play 'Hamlet'. The play was written in</t>
+        </is>
+      </c>
+      <c r="H186" t="b">
+        <v>1</v>
+      </c>
+      <c r="I186" t="n">
+        <v>1</v>
+      </c>
+      <c r="J186" t="n">
+        <v>1</v>
+      </c>
+      <c r="K186" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>[(' William', 1.0), (' Shakespeare', 1.0), (' wrote', 1.0), (' the', 1.0), (' play', 1.0), (" '", 1.0), ('Ham', 1.0), ('let', 1.0), ("'.", 1.0), (' The', 1.0), (' play', 1.0), (' was', 1.0), (' written', 1.0), (' in', 1.0), (' ', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M186" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>15</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>yes, you can. But you should be aware of the risks involved.</t>
+        </is>
+      </c>
+      <c r="H187" t="b">
+        <v>0</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0.0557</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0.8249</v>
+      </c>
+      <c r="K187" t="n">
+        <v>1.027600049972534</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' you', 0.5), (' should', 0.5), (' be', 1.0), (' aware', 1.0), (' of', 1.0), (' the', 1.0), (' risks', 1.0), (' involved', 1.0), ('.', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M187" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>15</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>it depends. The answer depends on the type of business you are in,</t>
+        </is>
+      </c>
+      <c r="H188" t="b">
+        <v>0</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0.9389</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0.5424000024795532</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M188" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>15</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="H189" t="b">
+        <v>0</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0.9389</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0.5424000024795532</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M189" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>15</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="H190" t="b">
+        <v>0</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0.9389</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0.5424000024795532</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M190" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>15</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>it depends. The answer depends on the type of business you are in,</t>
+        </is>
+      </c>
+      <c r="H191" t="b">
+        <v>0</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0.9389</v>
+      </c>
+      <c r="K191" t="n">
+        <v>0.5424000024795532</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M191" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>25</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>William Shakespeare wrote the play 'Hamlet'. The play was written in 1601. The play is about a prince who</t>
+        </is>
+      </c>
+      <c r="H192" t="b">
+        <v>1</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0.3465999960899353</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>[(' William', 1.0), (' Shakespeare', 1.0), (' wrote', 1.0), (' the', 1.0), (' play', 1.0), (" '", 1.0), ('Ham', 1.0), ('let', 1.0), ("'.", 1.0), (' The', 1.0), (' play', 1.0), (' was', 1.0), (' written', 1.0), (' in', 1.0), (' ', 1.0), ('160', 1.0), ('1', 1.0), ('.', 1.0), (' The', 1.0), (' play', 1.0), (' is', 1.0), (' about', 1.0), (' a', 1.0), (' prince', 1.0), (' who', 0.5)]</t>
+        </is>
+      </c>
+      <c r="M192" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>25</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>William Shakespeare wrote the play 'Hamlet'. The play was written in 1601. The play is about a prince who</t>
+        </is>
+      </c>
+      <c r="H193" t="b">
+        <v>1</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0.3465999960899353</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>[(' William', 1.0), (' Shakespeare', 1.0), (' wrote', 1.0), (' the', 1.0), (' play', 1.0), (" '", 1.0), ('Ham', 1.0), ('let', 1.0), ("'.", 1.0), (' The', 1.0), (' play', 1.0), (' was', 1.0), (' written', 1.0), (' in', 1.0), (' ', 1.0), ('160', 1.0), ('1', 1.0), ('.', 1.0), (' The', 1.0), (' play', 1.0), (' is', 1.0), (' about', 1.0), (' a', 1.0), (' prince', 1.0), (' who', 0.5)]</t>
+        </is>
+      </c>
+      <c r="M193" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>25</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>William Shakespeare wrote the play 'Hamlet'. The play was written in 1601. The play is about a prince who</t>
+        </is>
+      </c>
+      <c r="H194" t="b">
+        <v>1</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0.3465999960899353</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>[(' William', 1.0), (' Shakespeare', 1.0), (' wrote', 1.0), (' the', 1.0), (' play', 1.0), (" '", 1.0), ('Ham', 1.0), ('let', 1.0), ("'.", 1.0), (' The', 1.0), (' play', 1.0), (' was', 1.0), (' written', 1.0), (' in', 1.0), (' ', 1.0), ('160', 1.0), ('1', 1.0), ('.', 1.0), (' The', 1.0), (' play', 1.0), (' is', 1.0), (' about', 1.0), (' a', 1.0), (' prince', 1.0), (' who', 0.5)]</t>
+        </is>
+      </c>
+      <c r="M194" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>25</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>William Shakespeare wrote the play 'Hamlet'. The play was written in 1601. The play is about a prince named</t>
+        </is>
+      </c>
+      <c r="H195" t="b">
+        <v>1</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="K195" t="n">
+        <v>0.3465999960899353</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>[(' William', 1.0), (' Shakespeare', 1.0), (' wrote', 1.0), (' the', 1.0), (' play', 1.0), (" '", 1.0), ('Ham', 1.0), ('let', 1.0), ("'.", 1.0), (' The', 1.0), (' play', 1.0), (' was', 1.0), (' written', 1.0), (' in', 1.0), (' ', 1.0), ('160', 1.0), ('1', 1.0), ('.', 1.0), (' The', 1.0), (' play', 1.0), (' is', 1.0), (' about', 1.0), (' a', 1.0), (' prince', 1.0), (' named', 0.5)]</t>
+        </is>
+      </c>
+      <c r="M195" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>25</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>William Shakespeare wrote the play 'Hamlet'. The play was written in 1601. The play is about a prince named</t>
+        </is>
+      </c>
+      <c r="H196" t="b">
+        <v>1</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0.3465999960899353</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>[(' William', 1.0), (' Shakespeare', 1.0), (' wrote', 1.0), (' the', 1.0), (' play', 1.0), (" '", 1.0), ('Ham', 1.0), ('let', 1.0), ("'.", 1.0), (' The', 1.0), (' play', 1.0), (' was', 1.0), (' written', 1.0), (' in', 1.0), (' ', 1.0), ('160', 1.0), ('1', 1.0), ('.', 1.0), (' The', 1.0), (' play', 1.0), (' is', 1.0), (' about', 1.0), (' a', 1.0), (' prince', 1.0), (' named', 0.5)]</t>
+        </is>
+      </c>
+      <c r="M196" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>25</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>it depends. The</t>
+        </is>
+      </c>
+      <c r="H197" t="b">
+        <v>0</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0.9629</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0.5424000024795532</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M197" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>25</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>it depends. The answer depends on the type of business you are in, the type of customers you have, and the type</t>
+        </is>
+      </c>
+      <c r="H198" t="b">
+        <v>0</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0.9465</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0.8216000199317932</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' customers', 0.6514), (' you', 1.0), (' have', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' type', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M198" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>25</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>it depends. The</t>
+        </is>
+      </c>
+      <c r="H199" t="b">
+        <v>0</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0.9629</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0.5424000024795532</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M199" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>25</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>it depends. The answer depends on the type of business you are in, the type of customers you have, and the type</t>
+        </is>
+      </c>
+      <c r="H200" t="b">
+        <v>0</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0.9465</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0.8216000199317932</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' customers', 0.6514), (' you', 1.0), (' have', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' type', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M200" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Who wrote the play 'Hamlet'?</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>25</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>William Shakespeare</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>yes, you can. But it’s not as easy as it sounds. There are a few things you need to know before</t>
+        </is>
+      </c>
+      <c r="H201" t="b">
+        <v>0</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0.8665</v>
+      </c>
+      <c r="K201" t="n">
+        <v>1.374199986457825</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' it', 0.5), ('’s', 1.0), (' not', 1.0), (' as', 1.0), (' easy', 0.5), (' as', 1.0), (' it', 1.0), (' sounds', 1.0), ('.', 1.0), (' There', 0.5), (' are', 1.0), (' a', 1.0), (' few', 1.0), (' things', 1.0), (' you', 1.0), (' need', 1.0), (' to', 1.0), (' know', 1.0), (' before', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M201" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>15</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Bananas are yellow. They are not green, red, blue, or</t>
+        </is>
+      </c>
+      <c r="H202" t="b">
+        <v>1</v>
+      </c>
+      <c r="I202" t="n">
+        <v>0.09030000000000001</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0.8519</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0.9294000267982483</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>[(' Ban', 1.0), ('anas', 1.0), (' are', 1.0), (' yellow', 1.0), ('.', 1.0), (' They', 0.3486), (' are', 1.0), (' not', 1.0), (' green', 1.0), (',', 1.0), (' red', 0.3333), (',', 1.0), (' blue', 0.7773), (',', 1.0), (' or', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M202" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>15</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Bananas are yellow. They are not green, red, or blue.</t>
+        </is>
+      </c>
+      <c r="H203" t="b">
+        <v>1</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0.7838000000000001</v>
+      </c>
+      <c r="K203" t="n">
+        <v>1.068099975585938</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>[(' Ban', 1.0), ('anas', 1.0), (' are', 1.0), (' yellow', 1.0), ('.', 1.0), (' They', 0.3486), (' are', 1.0), (' not', 1.0), (' green', 1.0), (',', 1.0), (' red', 0.3333), (',', 1.0), (' or', 0.2227), (' blue', 1.0), ('.', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M203" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>15</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Bananas are yellow. They are not green, they are not brown,</t>
+        </is>
+      </c>
+      <c r="H204" t="b">
+        <v>1</v>
+      </c>
+      <c r="I204" t="n">
+        <v>0.1162</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0.8663</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0.7336000204086304</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>[(' Ban', 1.0), ('anas', 1.0), (' are', 1.0), (' yellow', 1.0), ('.', 1.0), (' They', 0.3486), (' are', 1.0), (' not', 1.0), (' green', 1.0), (',', 1.0), (' they', 0.3333), (' are', 1.0), (' not', 1.0), (' brown', 1.0), (',', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M204" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>15</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Bananas are yellow. But they’re not just yellow. They’re yellow</t>
+        </is>
+      </c>
+      <c r="H205" t="b">
+        <v>1</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0.6514</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0.9718</v>
+      </c>
+      <c r="K205" t="n">
+        <v>0.2791999876499176</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>[(' Ban', 1.0), ('anas', 1.0), (' are', 1.0), (' yellow', 1.0), ('.', 1.0), (' But', 0.6514), (' they', 1.0), ('’re', 1.0), (' not', 1.0), (' just', 1.0), (' yellow', 1.0), ('.', 1.0), (' They', 1.0), ('’re', 1.0), (' yellow', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M205" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>15</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Bananas are yellow. They are not green, red, blue, or</t>
+        </is>
+      </c>
+      <c r="H206" t="b">
+        <v>1</v>
+      </c>
+      <c r="I206" t="n">
+        <v>0.09030000000000001</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0.8519</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0.9294000267982483</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>[(' Ban', 1.0), ('anas', 1.0), (' are', 1.0), (' yellow', 1.0), ('.', 1.0), (' They', 0.3486), (' are', 1.0), (' not', 1.0), (' green', 1.0), (',', 1.0), (' red', 0.3333), (',', 1.0), (' blue', 0.7773), (',', 1.0), (' or', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M206" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>15</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>it depends. The answer depends on the type of business you are in,</t>
+        </is>
+      </c>
+      <c r="H207" t="b">
+        <v>0</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0.9389</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0.5424000024795532</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M207" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>15</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>it depends. The answer depends on the type of business you are in,</t>
+        </is>
+      </c>
+      <c r="H208" t="b">
+        <v>0</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0.9389</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0.5424000024795532</v>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M208" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>15</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="H209" t="b">
+        <v>0</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0.9389</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0.5424000024795532</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M209" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>15</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="H210" t="b">
+        <v>0</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0.9389</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0.5424000024795532</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M210" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>15</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>yes, you can. But it’s not as simple as it sounds.</t>
+        </is>
+      </c>
+      <c r="H211" t="b">
+        <v>0</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0.0557</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0.8249</v>
+      </c>
+      <c r="K211" t="n">
+        <v>1.027600049972534</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' it', 0.5), ('’s', 1.0), (' not', 1.0), (' as', 1.0), (' simple', 0.5), (' as', 1.0), (' it', 1.0), (' sounds', 1.0), ('.', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M211" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>25</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Bananas are yellow. They are not green, orange, or red. They are yellow.
+What is the primary color of</t>
+        </is>
+      </c>
+      <c r="H212" t="b">
+        <v>1</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0.0452</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0.8835</v>
+      </c>
+      <c r="K212" t="n">
+        <v>1.276000022888184</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>[(' Ban', 1.0), ('anas', 1.0), (' are', 1.0), (' yellow', 1.0), ('.', 1.0), (' They', 0.3486), (' are', 1.0), (' not', 1.0), (' green', 1.0), (',', 1.0), (' orange', 0.3333), (',', 1.0), (' or', 0.5), (' red', 0.7773), ('.', 1.0), (' They', 1.0), (' are', 1.0), (' yellow', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' primary', 1.0), (' color', 1.0), (' of', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M212" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>25</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Bananas are yellow. But they’re not just yellow. They’re yellow with a hint of green. And they’re yellow</t>
+        </is>
+      </c>
+      <c r="H213" t="b">
+        <v>1</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0.6514</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0.2791999876499176</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>[(' Ban', 1.0), ('anas', 1.0), (' are', 1.0), (' yellow', 1.0), ('.', 1.0), (' But', 0.6514), (' they', 1.0), ('’re', 1.0), (' not', 1.0), (' just', 1.0), (' yellow', 1.0), ('.', 1.0), (' They', 1.0), ('’re', 1.0), (' yellow', 1.0), (' with', 1.0), (' a', 1.0), (' hint', 1.0), (' of', 1.0), (' green', 1.0), ('.', 1.0), (' And', 1.0), (' they', 1.0), ('’re', 1.0), (' yellow', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M213" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>25</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Bananas are yellow. They are not green, orange, or red. They are yellow.
+What is the primary color of</t>
+        </is>
+      </c>
+      <c r="H214" t="b">
+        <v>1</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0.0452</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0.8835</v>
+      </c>
+      <c r="K214" t="n">
+        <v>1.276000022888184</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>[(' Ban', 1.0), ('anas', 1.0), (' are', 1.0), (' yellow', 1.0), ('.', 1.0), (' They', 0.3486), (' are', 1.0), (' not', 1.0), (' green', 1.0), (',', 1.0), (' orange', 0.3333), (',', 1.0), (' or', 0.5), (' red', 0.7773), ('.', 1.0), (' They', 1.0), (' are', 1.0), (' yellow', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' primary', 1.0), (' color', 1.0), (' of', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M214" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>25</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Bananas are yellow. But they’re not just yellow. They’re yellow with a hint of green. And they’re yellow</t>
+        </is>
+      </c>
+      <c r="H215" t="b">
+        <v>1</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0.6514</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0.2791999876499176</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>[(' Ban', 1.0), ('anas', 1.0), (' are', 1.0), (' yellow', 1.0), ('.', 1.0), (' But', 0.6514), (' they', 1.0), ('’re', 1.0), (' not', 1.0), (' just', 1.0), (' yellow', 1.0), ('.', 1.0), (' They', 1.0), ('’re', 1.0), (' yellow', 1.0), (' with', 1.0), (' a', 1.0), (' hint', 1.0), (' of', 1.0), (' green', 1.0), ('.', 1.0), (' And', 1.0), (' they', 1.0), ('’re', 1.0), (' yellow', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M215" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>25</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Bananas are yellow. But they’re not just yellow. They’re yellow with a hint of green. And they’re yellow</t>
+        </is>
+      </c>
+      <c r="H216" t="b">
+        <v>1</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0.6514</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0.2791999876499176</v>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>[(' Ban', 1.0), ('anas', 1.0), (' are', 1.0), (' yellow', 1.0), ('.', 1.0), (' But', 0.6514), (' they', 1.0), ('’re', 1.0), (' not', 1.0), (' just', 1.0), (' yellow', 1.0), ('.', 1.0), (' They', 1.0), ('’re', 1.0), (' yellow', 1.0), (' with', 1.0), (' a', 1.0), (' hint', 1.0), (' of', 1.0), (' green', 1.0), ('.', 1.0), (' And', 1.0), (' they', 1.0), ('’re', 1.0), (' yellow', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M216" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>25</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>it depends. The</t>
+        </is>
+      </c>
+      <c r="H217" t="b">
+        <v>0</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0.9629</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0.5424000024795532</v>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M217" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>25</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>yes, you can. But it’s not as simple as it sounds. There are a few things you need to know before</t>
+        </is>
+      </c>
+      <c r="H218" t="b">
+        <v>0</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0.0557</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0.8909</v>
+      </c>
+      <c r="K218" t="n">
+        <v>1.027600049972534</v>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' it', 0.5), ('’s', 1.0), (' not', 1.0), (' as', 1.0), (' simple', 0.5), (' as', 1.0), (' it', 1.0), (' sounds', 1.0), ('.', 1.0), (' There', 1.0), (' are', 1.0), (' a', 1.0), (' few', 1.0), (' things', 1.0), (' you', 1.0), (' need', 1.0), (' to', 1.0), (' know', 1.0), (' before', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M218" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>25</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>it depends. The</t>
+        </is>
+      </c>
+      <c r="H219" t="b">
+        <v>0</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0.9629</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0.5424000024795532</v>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M219" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>25</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>it depends. The</t>
+        </is>
+      </c>
+      <c r="H220" t="b">
+        <v>0</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0.9629</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0.5424000024795532</v>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M220" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>What is the primary color of bananas?</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>25</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>it depends. The answer depends on the type of business you are in, the type of customers you have, and the type</t>
+        </is>
+      </c>
+      <c r="H221" t="b">
+        <v>0</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0.9465</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0.8216000199317932</v>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' customers', 0.6514), (' you', 1.0), (' have', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' type', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M221" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>15</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>George</t>
+        </is>
+      </c>
+      <c r="H222" t="b">
+        <v>0</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0.9548</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0.3465999960899353</v>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>[(' George', 1.0), (' Orwell', 1.0), ('\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('198', 0.5), ('4', 1.0), ("'?", 1.0), (' Fact', 1.0), (':', 1.0), (' George', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M222" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>15</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>George</t>
+        </is>
+      </c>
+      <c r="H223" t="b">
+        <v>0</v>
+      </c>
+      <c r="I223" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0.9548</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0.3465999960899353</v>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>[(' George', 1.0), (' Orwell', 1.0), ('\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('198', 0.5), ('4', 1.0), ("'?", 1.0), (' Fact', 1.0), (':', 1.0), (' George', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M223" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>15</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>George</t>
+        </is>
+      </c>
+      <c r="H224" t="b">
+        <v>0</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0.9548</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0.3465999960899353</v>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>[(' George', 1.0), (' Orwell', 1.0), ('\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('198', 0.5), ('4', 1.0), ("'?", 1.0), (' Fact', 1.0), (':', 1.0), (' George', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M224" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>15</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>George</t>
+        </is>
+      </c>
+      <c r="H225" t="b">
+        <v>0</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0.9548</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0.3465999960899353</v>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>[(' George', 1.0), (' Orwell', 1.0), ('\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('Animal', 0.5), (' Farm', 1.0), ("'?", 1.0), (' Fact', 1.0), (':', 1.0), (' George', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M225" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>15</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>George</t>
+        </is>
+      </c>
+      <c r="H226" t="b">
+        <v>0</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0.9548</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0.3465999960899353</v>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>[(' George', 1.0), (' Orwell', 1.0), ('\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('198', 0.5), ('4', 1.0), ("'?", 1.0), (' Fact', 1.0), (':', 1.0), (' George', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M226" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>15</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>yes, you can. But it’s not as simple as it sounds.</t>
+        </is>
+      </c>
+      <c r="H227" t="b">
+        <v>0</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0.0557</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0.8249</v>
+      </c>
+      <c r="K227" t="n">
+        <v>1.027600049972534</v>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' it', 0.5), ('’s', 1.0), (' not', 1.0), (' as', 1.0), (' simple', 0.5), (' as', 1.0), (' it', 1.0), (' sounds', 1.0), ('.', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M227" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>15</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="H228" t="b">
+        <v>0</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0.9389</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0.5424000024795532</v>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M228" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>15</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>it depends. The answer depends on the type of business you are in,</t>
+        </is>
+      </c>
+      <c r="H229" t="b">
+        <v>0</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0.9389</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0.5424000024795532</v>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M229" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>15</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>yes, you can. But it’s not as easy as it sounds.</t>
+        </is>
+      </c>
+      <c r="H230" t="b">
+        <v>0</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0.0557</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0.8249</v>
+      </c>
+      <c r="K230" t="n">
+        <v>1.027600049972534</v>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' it', 0.5), ('’s', 1.0), (' not', 1.0), (' as', 1.0), (' easy', 0.5), (' as', 1.0), (' it', 1.0), (' sounds', 1.0), ('.', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M230" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>15</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>it depends. The answer depends on the type of business you are in,</t>
+        </is>
+      </c>
+      <c r="H231" t="b">
+        <v>0</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0.9389</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0.5424000024795532</v>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M231" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>25</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>George Orwell
+Who is the author of '1984</t>
+        </is>
+      </c>
+      <c r="H232" t="b">
+        <v>1</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="K232" t="n">
+        <v>0.3465999960899353</v>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>[(' George', 1.0), (' Orwell', 1.0), ('\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('198', 0.5), ('4', 1.0), ("'?", 1.0), (' Fact', 1.0), (':', 1.0), (' George', 1.0), (' Orwell', 1.0), ('\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('198', 1.0), ('4', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M232" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>25</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>George Orwell
+Who is the author of 'The Road</t>
+        </is>
+      </c>
+      <c r="H233" t="b">
+        <v>1</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="K233" t="n">
+        <v>0.3465999960899353</v>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>[(' George', 1.0), (' Orwell', 1.0), ('\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('Animal', 0.5), (' Farm', 1.0), ("'?", 1.0), (' Fact', 1.0), (':', 1.0), (' George', 1.0), (' Orwell', 1.0), ('\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('The', 1.0), (' Road', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M233" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>25</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>George Orwell
+Who is the author of 'The Road</t>
+        </is>
+      </c>
+      <c r="H234" t="b">
+        <v>1</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0.3465999960899353</v>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>[(' George', 1.0), (' Orwell', 1.0), ('\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('Animal', 0.5), (' Farm', 1.0), ("'?", 1.0), (' Fact', 1.0), (':', 1.0), (' George', 1.0), (' Orwell', 1.0), ('\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('The', 1.0), (' Road', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M234" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>25</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>George Orwell
+Who is the author of 'The Road</t>
+        </is>
+      </c>
+      <c r="H235" t="b">
+        <v>1</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="K235" t="n">
+        <v>0.3465999960899353</v>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>[(' George', 1.0), (' Orwell', 1.0), ('\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('Animal', 0.5), (' Farm', 1.0), ("'?", 1.0), (' Fact', 1.0), (':', 1.0), (' George', 1.0), (' Orwell', 1.0), ('\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('The', 1.0), (' Road', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M235" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>25</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Fact Statement</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>George Orwell
+Who is the author of '1984</t>
+        </is>
+      </c>
+      <c r="H236" t="b">
+        <v>1</v>
+      </c>
+      <c r="I236" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0.3465999960899353</v>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>[(' George', 1.0), (' Orwell', 1.0), ('\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('198', 0.5), ('4', 1.0), ("'?", 1.0), (' Fact', 1.0), (':', 1.0), (' George', 1.0), (' Orwell', 1.0), ('\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('198', 1.0), ('4', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M236" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>25</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>it depends. The</t>
+        </is>
+      </c>
+      <c r="H237" t="b">
+        <v>0</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0.9629</v>
+      </c>
+      <c r="K237" t="n">
+        <v>0.5424000024795532</v>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 0.5), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' it', 1.0), (' depends', 1.0), ('.', 1.0), (' The', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M237" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>25</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>yes, you can. But it’s not as simple as it sounds. There are a few things you need to know before</t>
+        </is>
+      </c>
+      <c r="H238" t="b">
+        <v>0</v>
+      </c>
+      <c r="I238" t="n">
+        <v>0.0557</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0.8909</v>
+      </c>
+      <c r="K238" t="n">
+        <v>1.027600049972534</v>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' it', 0.5), ('’s', 1.0), (' not', 1.0), (' as', 1.0), (' simple', 0.5), (' as', 1.0), (' it', 1.0), (' sounds', 1.0), ('.', 1.0), (' There', 1.0), (' are', 1.0), (' a', 1.0), (' few', 1.0), (' things', 1.0), (' you', 1.0), (' need', 1.0), (' to', 1.0), (' know', 1.0), (' before', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M238" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>25</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>it depends. The answer depends on the type of business you are in, the type of business you want to be in,</t>
+        </is>
+      </c>
+      <c r="H239" t="b">
+        <v>0</v>
+      </c>
+      <c r="I239" t="n">
+        <v>0.0678</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0.8979</v>
+      </c>
+      <c r="K239" t="n">
+        <v>1.25629997253418</v>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 0.3486), (' you', 1.0), (' want', 0.5), (' to', 1.0), (' be', 1.0), (' in', 1.0), (',', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M239" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>25</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>yes, you can. But you need to be careful. You need to know what you are doing. You need to know</t>
+        </is>
+      </c>
+      <c r="H240" t="b">
+        <v>0</v>
+      </c>
+      <c r="I240" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0.8428</v>
+      </c>
+      <c r="K240" t="n">
+        <v>1.720800042152405</v>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>[(' yes', 0.2227), (',', 1.0), (' you', 1.0), (' can', 1.0), ('.', 1.0), (' But', 1.0), (' you', 0.5), (' need', 0.5), (' to', 1.0), (' be', 1.0), (' careful', 1.0), ('.', 1.0), (' You', 0.5), (' need', 1.0), (' to', 1.0), (' know', 0.5), (' what', 1.0), (' you', 1.0), (' are', 1.0), (' doing', 1.0), ('.', 1.0), (' You', 1.0), (' need', 1.0), (' to', 1.0), (' know', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M240" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Who is the author of '1984'?</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>25</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>George Orwell</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>it depends. The answer depends on the type of business you are in, the type of customers you have, and the type</t>
+        </is>
+      </c>
+      <c r="H241" t="b">
+        <v>0</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0.9465</v>
+      </c>
+      <c r="K241" t="n">
+        <v>0.8216000199317932</v>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>[(' it', 0.7773), (' depends', 1.0), ('.', 1.0), (' The', 1.0), (' answer', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' business', 1.0), (' you', 1.0), (' are', 1.0), (' in', 1.0), (',', 1.0), (' the', 1.0), (' type', 1.0), (' of', 1.0), (' customers', 0.6514), (' you', 1.0), (' have', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' type', 1.0)]</t>
+        </is>
+      </c>
+      <c r="M241" t="n">
         <v>5</v>
       </c>
     </row>
